--- a/results/-1Fold_SAC_ours.xlsx
+++ b/results/-1Fold_SAC_ours.xlsx
@@ -574,22 +574,22 @@
         <v>2000</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5556963407493501</v>
+        <v>0.5478623653329366</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5542297279923835</v>
+        <v>0.5463322681746202</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5741572912643146</v>
+        <v>0.5633974751119114</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.217198759326847</v>
+        <v>0.2192656447422918</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001835964811775356</v>
+        <v>0.001847505060873771</v>
       </c>
       <c r="S2" t="n">
-        <v>11.14377593994141</v>
+        <v>11.05035781860352</v>
       </c>
     </row>
     <row r="3">
@@ -641,22 +641,22 @@
         <v>2000</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5612250597145164</v>
+        <v>0.5578383961620231</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5622628769227035</v>
+        <v>0.559658900304519</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5802523423185114</v>
+        <v>0.5758505005186029</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2036378170546291</v>
+        <v>0.2044121496817272</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001929825441175998</v>
+        <v>0.001870397664627033</v>
       </c>
       <c r="S3" t="n">
-        <v>11.016974568367</v>
+        <v>11.02047741413116</v>
       </c>
     </row>
     <row r="4">
@@ -708,22 +708,22 @@
         <v>2000</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6034812998924385</v>
+        <v>0.5998856502226462</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5960915408903257</v>
+        <v>0.5929666092872614</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6403845953648946</v>
+        <v>0.6358360376326286</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2120765676028419</v>
+        <v>0.214383741035354</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00297328259574069</v>
+        <v>0.001915264005137589</v>
       </c>
       <c r="S4" t="n">
-        <v>12.95329964160919</v>
+        <v>10.97910332679749</v>
       </c>
     </row>
     <row r="5">
@@ -775,22 +775,22 @@
         <v>2000</v>
       </c>
       <c r="N5" t="n">
-        <v>0.626811246942692</v>
+        <v>0.6235108541293687</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6217490417047598</v>
+        <v>0.6188391833289462</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6710700188993395</v>
+        <v>0.6665121315752414</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2040876709955019</v>
+        <v>0.2064116708853574</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004261102239546174</v>
+        <v>0.001860646879382033</v>
       </c>
       <c r="S5" t="n">
-        <v>15.61295127868652</v>
+        <v>10.88275170326233</v>
       </c>
     </row>
     <row r="6">
@@ -842,22 +842,22 @@
         <v>2000</v>
       </c>
       <c r="N6" t="n">
-        <v>0.655008672368227</v>
+        <v>0.6563363856414329</v>
       </c>
       <c r="O6" t="n">
-        <v>0.652504877280233</v>
+        <v>0.6539485358173016</v>
       </c>
       <c r="P6" t="n">
-        <v>0.696938347710724</v>
+        <v>0.6982476270094335</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1982122000755238</v>
+        <v>0.1987034045458829</v>
       </c>
       <c r="R6" t="n">
-        <v>0.004731199514621614</v>
+        <v>0.001833945666759111</v>
       </c>
       <c r="S6" t="n">
-        <v>16.44697284698486</v>
+        <v>10.78181743621826</v>
       </c>
     </row>
     <row r="7">
@@ -909,22 +909,22 @@
         <v>2000</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6783679415049321</v>
+        <v>0.6780181761285677</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6680309472394018</v>
+        <v>0.6679678340608525</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7283944478982108</v>
+        <v>0.7274804495257164</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2080626908886993</v>
+        <v>0.2015321954380749</v>
       </c>
       <c r="R7" t="n">
-        <v>0.005030513253684667</v>
+        <v>0.001844616692757856</v>
       </c>
       <c r="S7" t="n">
-        <v>16.590700507164</v>
+        <v>10.70443308353424</v>
       </c>
     </row>
     <row r="8">
@@ -976,22 +976,22 @@
         <v>2000</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5477480435214342</v>
+        <v>0.5479092665889376</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5460899283381441</v>
+        <v>0.5463763836562562</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5633198075478525</v>
+        <v>0.5634687705494987</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2187698370697578</v>
+        <v>0.219019675546355</v>
       </c>
       <c r="R8" t="n">
-        <v>0.01127587399729993</v>
+        <v>0.009857994320929207</v>
       </c>
       <c r="S8" t="n">
-        <v>9.223087310791016</v>
+        <v>8.771037697792053</v>
       </c>
     </row>
     <row r="9">
@@ -1043,22 +1043,22 @@
         <v>2000</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5566016728043446</v>
+        <v>0.5577905229997904</v>
       </c>
       <c r="O9" t="n">
-        <v>0.558109147970135</v>
+        <v>0.5596092170757048</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5743277328511456</v>
+        <v>0.5758042330864944</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2040812640811956</v>
+        <v>0.2041965328291446</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01107669170636581</v>
+        <v>0.009993643769055498</v>
       </c>
       <c r="S9" t="n">
-        <v>9.060075879096985</v>
+        <v>8.712206125259399</v>
       </c>
     </row>
     <row r="10">
@@ -1110,22 +1110,22 @@
         <v>2000</v>
       </c>
       <c r="N10" t="n">
-        <v>0.60361216530471</v>
+        <v>0.6001109906651672</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5965204443158995</v>
+        <v>0.5931308963884582</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6405739631626536</v>
+        <v>0.6361063358464418</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2128061939561868</v>
+        <v>0.2141118800657035</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01275338336568634</v>
+        <v>0.01020483481994077</v>
       </c>
       <c r="S10" t="n">
-        <v>9.375443577766418</v>
+        <v>8.656876683235168</v>
       </c>
     </row>
     <row r="11">
@@ -1177,22 +1177,22 @@
         <v>2000</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6227272760528736</v>
+        <v>0.6234654929335305</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6178266709753747</v>
+        <v>0.6185634009473063</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6658760697126709</v>
+        <v>0.6668374149192691</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2059483876704978</v>
+        <v>0.2059887618505567</v>
       </c>
       <c r="R11" t="n">
-        <v>0.01180634038843718</v>
+        <v>0.009914033570624583</v>
       </c>
       <c r="S11" t="n">
-        <v>9.098377108573914</v>
+        <v>8.580996155738831</v>
       </c>
     </row>
     <row r="12">
@@ -1244,22 +1244,22 @@
         <v>2000</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6500149293652093</v>
+        <v>0.6565831091458847</v>
       </c>
       <c r="O12" t="n">
-        <v>0.647545769573914</v>
+        <v>0.6541425694392642</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6906266604764949</v>
+        <v>0.6983766135349954</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2005659774506363</v>
+        <v>0.1986620076294977</v>
       </c>
       <c r="R12" t="n">
-        <v>0.01082544418290589</v>
+        <v>0.009762954406456394</v>
       </c>
       <c r="S12" t="n">
-        <v>8.599316358566284</v>
+        <v>8.471821427345276</v>
       </c>
     </row>
     <row r="13">
@@ -1311,22 +1311,22 @@
         <v>2000</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6608041758849356</v>
+        <v>0.6781852173614925</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6508730893778821</v>
+        <v>0.6682141637486445</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7072864428932566</v>
+        <v>0.7276235207075175</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2072598127068224</v>
+        <v>0.2013524895182235</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01018694272373581</v>
+        <v>0.009819069332820531</v>
       </c>
       <c r="S13" t="n">
-        <v>8.208976745605469</v>
+        <v>8.413897633552551</v>
       </c>
     </row>
     <row r="14">
@@ -1378,22 +1378,22 @@
         <v>2000</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5476366530384319</v>
+        <v>0.5480030691009395</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5461345355692707</v>
+        <v>0.5464535002304582</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5632118584650141</v>
+        <v>0.5636553074671399</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2182119349548731</v>
+        <v>0.2179938615910029</v>
       </c>
       <c r="R14" t="n">
-        <v>0.03202627061954087</v>
+        <v>0.03218438149356286</v>
       </c>
       <c r="S14" t="n">
-        <v>7.006830751895905</v>
+        <v>7.041582405567169</v>
       </c>
     </row>
     <row r="15">
@@ -1445,22 +1445,22 @@
         <v>2000</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5577977765092196</v>
+        <v>0.5576527063206356</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5595036120997735</v>
+        <v>0.5594764978926795</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5759346497800127</v>
+        <v>0.5755909565729004</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2033735049459105</v>
+        <v>0.2033234007735613</v>
       </c>
       <c r="R15" t="n">
-        <v>0.03247548719725043</v>
+        <v>0.03266448367982066</v>
       </c>
       <c r="S15" t="n">
-        <v>6.921159327030182</v>
+        <v>6.960592806339264</v>
       </c>
     </row>
     <row r="16">
@@ -1512,22 +1512,22 @@
         <v>2000</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6020431799875293</v>
+        <v>0.6015743039114761</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5950394034655351</v>
+        <v>0.5944736556507981</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6389583983235786</v>
+        <v>0.6380852117308297</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2125328727866501</v>
+        <v>0.2130134896661829</v>
       </c>
       <c r="R16" t="n">
-        <v>0.03291161692695217</v>
+        <v>0.03325335964083979</v>
       </c>
       <c r="S16" t="n">
-        <v>6.814522862434387</v>
+        <v>6.894373297691345</v>
       </c>
     </row>
     <row r="17">
@@ -1579,22 +1579,22 @@
         <v>2000</v>
       </c>
       <c r="N17" t="n">
-        <v>0.624457586184443</v>
+        <v>0.6263316620415318</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6194550261542995</v>
+        <v>0.6213924369455294</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6684317907950394</v>
+        <v>0.6705214453565553</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.2038341272185351</v>
+        <v>0.2045855019876129</v>
       </c>
       <c r="R17" t="n">
-        <v>0.03182631882395019</v>
+        <v>0.03229164110484834</v>
       </c>
       <c r="S17" t="n">
-        <v>6.713589549064636</v>
+        <v>6.82518482208252</v>
       </c>
     </row>
     <row r="18">
@@ -1646,22 +1646,22 @@
         <v>2000</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6573677343447268</v>
+        <v>0.6550242315081475</v>
       </c>
       <c r="O18" t="n">
-        <v>0.654763507863815</v>
+        <v>0.6527477305372049</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6998183661840732</v>
+        <v>0.6964023117161647</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1985522396402109</v>
+        <v>0.1981126780602775</v>
       </c>
       <c r="R18" t="n">
-        <v>0.03084116393508609</v>
+        <v>0.03179350142033732</v>
       </c>
       <c r="S18" t="n">
-        <v>6.463162243366241</v>
+        <v>6.725987732410431</v>
       </c>
     </row>
     <row r="19">
@@ -1713,22 +1713,22 @@
         <v>2000</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6766942467060417</v>
+        <v>0.6783143278341025</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6664529147466068</v>
+        <v>0.6683528662709897</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7262269974164061</v>
+        <v>0.7278259493884843</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.2060563055409869</v>
+        <v>0.2005389005081051</v>
       </c>
       <c r="R19" t="n">
-        <v>0.03095501069228508</v>
+        <v>0.031964812748175</v>
       </c>
       <c r="S19" t="n">
-        <v>6.340717434883118</v>
+        <v>6.67863529920578</v>
       </c>
     </row>
     <row r="20">
@@ -1780,22 +1780,22 @@
         <v>2000</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5479217247350628</v>
+        <v>0.5482463693664447</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5464032730174557</v>
+        <v>0.5466653643657713</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5635786596409419</v>
+        <v>0.5640704275912283</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2171954491648486</v>
+        <v>0.2161363765750196</v>
       </c>
       <c r="R20" t="n">
-        <v>0.07092137174224789</v>
+        <v>0.07215525354428483</v>
       </c>
       <c r="S20" t="n">
-        <v>5.712569773197174</v>
+        <v>5.784955143928528</v>
       </c>
     </row>
     <row r="21">
@@ -1847,22 +1847,22 @@
         <v>2000</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5576722907960944</v>
+        <v>0.5586239512332054</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5594218598071437</v>
+        <v>0.560289338347786</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5758156930610009</v>
+        <v>0.5770162469084091</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2021843335040731</v>
+        <v>0.2016317835920086</v>
       </c>
       <c r="R21" t="n">
-        <v>0.07204425714474366</v>
+        <v>0.07329649523874147</v>
       </c>
       <c r="S21" t="n">
-        <v>5.612171113491058</v>
+        <v>5.688608467578888</v>
       </c>
     </row>
     <row r="22">
@@ -1914,22 +1914,22 @@
         <v>2000</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6012677849244444</v>
+        <v>0.6022580232044671</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5941142037769067</v>
+        <v>0.5952267501806113</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6377630285923809</v>
+        <v>0.6389058203125086</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.2114733981642291</v>
+        <v>0.211228551976669</v>
       </c>
       <c r="R22" t="n">
-        <v>0.07266904930127911</v>
+        <v>0.0744020976022266</v>
       </c>
       <c r="S22" t="n">
-        <v>5.502686321735382</v>
+        <v>5.617988407611847</v>
       </c>
     </row>
     <row r="23">
@@ -1981,22 +1981,22 @@
         <v>2000</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6252726244451484</v>
+        <v>0.6243178444359738</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6200787708067766</v>
+        <v>0.61949164011429</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6695459489699668</v>
+        <v>0.6680496961897814</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2022854933336632</v>
+        <v>0.203606082943696</v>
       </c>
       <c r="R23" t="n">
-        <v>0.07010709869961977</v>
+        <v>0.0723623023516945</v>
       </c>
       <c r="S23" t="n">
-        <v>5.409562408924103</v>
+        <v>5.563734710216522</v>
       </c>
     </row>
     <row r="24">
@@ -2048,22 +2048,22 @@
         <v>2000</v>
       </c>
       <c r="N24" t="n">
-        <v>0.6569587512382482</v>
+        <v>0.6567394414565133</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6542859587629856</v>
+        <v>0.6543387510436899</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6993183376114749</v>
+        <v>0.6985232281452097</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1968506169530991</v>
+        <v>0.1964654401297391</v>
       </c>
       <c r="R24" t="n">
-        <v>0.06784825410966173</v>
+        <v>0.07103374620698644</v>
       </c>
       <c r="S24" t="n">
-        <v>5.196805775165558</v>
+        <v>5.455926179885864</v>
       </c>
     </row>
     <row r="25">
@@ -2115,22 +2115,22 @@
         <v>2000</v>
       </c>
       <c r="N25" t="n">
-        <v>0.678783356274149</v>
+        <v>0.6777373426146986</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6683997121766903</v>
+        <v>0.6678384223394508</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7287824062048033</v>
+        <v>0.7270921200082666</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.2040605877706367</v>
+        <v>0.1993357857425274</v>
       </c>
       <c r="R25" t="n">
-        <v>0.06829734496859513</v>
+        <v>0.07144679521950389</v>
       </c>
       <c r="S25" t="n">
-        <v>5.113556504249573</v>
+        <v>5.422340035438538</v>
       </c>
     </row>
     <row r="26">
@@ -2182,22 +2182,22 @@
         <v>2000</v>
       </c>
       <c r="N26" t="n">
-        <v>0.5478348841282485</v>
+        <v>0.5483225839074463</v>
       </c>
       <c r="O26" t="n">
-        <v>0.5463549476250827</v>
+        <v>0.5467659296680872</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5635435290428802</v>
+        <v>0.5642618640787644</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.2163449174401277</v>
+        <v>0.2147568257614955</v>
       </c>
       <c r="R26" t="n">
-        <v>0.110248917581757</v>
+        <v>0.1143847700623671</v>
       </c>
       <c r="S26" t="n">
-        <v>4.915872097015381</v>
+        <v>5.036453783512115</v>
       </c>
     </row>
     <row r="27">
@@ -2249,22 +2249,22 @@
         <v>2000</v>
       </c>
       <c r="N27" t="n">
-        <v>0.5574209566943726</v>
+        <v>0.5584288318295599</v>
       </c>
       <c r="O27" t="n">
-        <v>0.5592538320514588</v>
+        <v>0.5601257008027846</v>
       </c>
       <c r="P27" t="n">
-        <v>0.5754608031063856</v>
+        <v>0.5766778301747828</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.2010126140402913</v>
+        <v>0.1999542697249449</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1121567551138393</v>
+        <v>0.1161600161447616</v>
       </c>
       <c r="S27" t="n">
-        <v>4.808412313461304</v>
+        <v>4.933507084846497</v>
       </c>
     </row>
     <row r="28">
@@ -2316,22 +2316,22 @@
         <v>2000</v>
       </c>
       <c r="N28" t="n">
-        <v>0.6004895906012041</v>
+        <v>0.6038200103712589</v>
       </c>
       <c r="O28" t="n">
-        <v>0.5934099720285734</v>
+        <v>0.5966025115010432</v>
       </c>
       <c r="P28" t="n">
-        <v>0.6366501453200649</v>
+        <v>0.6405345824957444</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.2104379852499763</v>
+        <v>0.2102156917855695</v>
       </c>
       <c r="R28" t="n">
-        <v>0.1126173913557531</v>
+        <v>0.1178213851644134</v>
       </c>
       <c r="S28" t="n">
-        <v>4.697565376758575</v>
+        <v>4.860002756118774</v>
       </c>
     </row>
     <row r="29">
@@ -2383,22 +2383,22 @@
         <v>2000</v>
       </c>
       <c r="N29" t="n">
-        <v>0.626253011581006</v>
+        <v>0.6230235870902037</v>
       </c>
       <c r="O29" t="n">
-        <v>0.6212456846949296</v>
+        <v>0.6183813230937341</v>
       </c>
       <c r="P29" t="n">
-        <v>0.6702357151253989</v>
+        <v>0.6665432352844576</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.2016006278467123</v>
+        <v>0.2027669127625342</v>
       </c>
       <c r="R29" t="n">
-        <v>0.1085523541575509</v>
+        <v>0.1145867384515295</v>
       </c>
       <c r="S29" t="n">
-        <v>4.597598195075989</v>
+        <v>4.813888549804688</v>
       </c>
     </row>
     <row r="30">
@@ -2450,22 +2450,22 @@
         <v>2000</v>
       </c>
       <c r="N30" t="n">
-        <v>0.6565179089405041</v>
+        <v>0.6571854701342309</v>
       </c>
       <c r="O30" t="n">
-        <v>0.6538925229999866</v>
+        <v>0.6547622339691094</v>
       </c>
       <c r="P30" t="n">
-        <v>0.6987183886724736</v>
+        <v>0.6992559344053613</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1956113133256153</v>
+        <v>0.1955328364813919</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1048260696633074</v>
+        <v>0.1121997792178948</v>
       </c>
       <c r="S30" t="n">
-        <v>4.420979976654053</v>
+        <v>4.701142847537994</v>
       </c>
     </row>
     <row r="31">
@@ -2517,22 +2517,22 @@
         <v>2000</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6785455595844831</v>
+        <v>0.6780619423904695</v>
       </c>
       <c r="O31" t="n">
-        <v>0.6682488584088619</v>
+        <v>0.6681524682970809</v>
       </c>
       <c r="P31" t="n">
-        <v>0.7284348647109353</v>
+        <v>0.7274756323323801</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.2025248838506326</v>
+        <v>0.1984761284353964</v>
       </c>
       <c r="R31" t="n">
-        <v>0.1055254451212968</v>
+        <v>0.1125919989538979</v>
       </c>
       <c r="S31" t="n">
-        <v>4.354442417621613</v>
+        <v>4.664197266101837</v>
       </c>
     </row>
     <row r="32">
@@ -2584,22 +2584,22 @@
         <v>2000</v>
       </c>
       <c r="N32" t="n">
-        <v>0.548214124752944</v>
+        <v>0.5486692135025785</v>
       </c>
       <c r="O32" t="n">
-        <v>0.5467299318907219</v>
+        <v>0.5471066044468476</v>
       </c>
       <c r="P32" t="n">
-        <v>0.5641824212215375</v>
+        <v>0.5649955904121612</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.2164503301121378</v>
+        <v>0.2141554864650335</v>
       </c>
       <c r="R32" t="n">
-        <v>0.1522847615526675</v>
+        <v>0.1642192100284234</v>
       </c>
       <c r="S32" t="n">
-        <v>4.174503922462463</v>
+        <v>4.374474942684174</v>
       </c>
     </row>
     <row r="33">
@@ -2651,22 +2651,22 @@
         <v>2000</v>
       </c>
       <c r="N33" t="n">
-        <v>0.5572370802303425</v>
+        <v>0.5566640529854356</v>
       </c>
       <c r="O33" t="n">
-        <v>0.5590133694505439</v>
+        <v>0.5584651084597562</v>
       </c>
       <c r="P33" t="n">
-        <v>0.5751658202170915</v>
+        <v>0.574299131542349</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.2005197289378934</v>
+        <v>0.199016822451134</v>
       </c>
       <c r="R33" t="n">
-        <v>0.1546507203946906</v>
+        <v>0.1663187144157331</v>
       </c>
       <c r="S33" t="n">
-        <v>4.058366328477859</v>
+        <v>4.270308077335358</v>
       </c>
     </row>
     <row r="34">
@@ -2718,22 +2718,22 @@
         <v>2000</v>
       </c>
       <c r="N34" t="n">
-        <v>0.6027940815242532</v>
+        <v>0.6034253146893276</v>
       </c>
       <c r="O34" t="n">
-        <v>0.5955948307499505</v>
+        <v>0.5960752541683308</v>
       </c>
       <c r="P34" t="n">
-        <v>0.6396898783635439</v>
+        <v>0.6402511215295449</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.20871544856871</v>
+        <v>0.2097429357801893</v>
       </c>
       <c r="R34" t="n">
-        <v>0.1538196383318129</v>
+        <v>0.1686313957100532</v>
       </c>
       <c r="S34" t="n">
-        <v>3.945062696933746</v>
+        <v>4.198080539703369</v>
       </c>
     </row>
     <row r="35">
@@ -2785,22 +2785,22 @@
         <v>2000</v>
       </c>
       <c r="N35" t="n">
-        <v>0.6263020309377988</v>
+        <v>0.6258989016005917</v>
       </c>
       <c r="O35" t="n">
-        <v>0.6212640947003106</v>
+        <v>0.6208106755346536</v>
       </c>
       <c r="P35" t="n">
-        <v>0.6703253619233989</v>
+        <v>0.6702407614904795</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1998795547052036</v>
+        <v>0.2017031386137546</v>
       </c>
       <c r="R35" t="n">
-        <v>0.1481354518741566</v>
+        <v>0.1637286612703384</v>
       </c>
       <c r="S35" t="n">
-        <v>3.859028100967407</v>
+        <v>4.146270275115967</v>
       </c>
     </row>
     <row r="36">
@@ -2852,22 +2852,22 @@
         <v>2000</v>
       </c>
       <c r="N36" t="n">
-        <v>0.6577811629197541</v>
+        <v>0.6586584020466937</v>
       </c>
       <c r="O36" t="n">
-        <v>0.6550002368997675</v>
+        <v>0.656069194765351</v>
       </c>
       <c r="P36" t="n">
-        <v>0.7001997714753484</v>
+        <v>0.7011125143345945</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.1948723718308163</v>
+        <v>0.1946243461559793</v>
       </c>
       <c r="R36" t="n">
-        <v>0.1423044282004755</v>
+        <v>0.1594296752640892</v>
       </c>
       <c r="S36" t="n">
-        <v>3.689152449369431</v>
+        <v>4.027722060680389</v>
       </c>
     </row>
     <row r="37">
@@ -2919,22 +2919,22 @@
         <v>2000</v>
       </c>
       <c r="N37" t="n">
-        <v>0.6787738735840703</v>
+        <v>0.6781443688503843</v>
       </c>
       <c r="O37" t="n">
-        <v>0.6685229214162206</v>
+        <v>0.6682647903707294</v>
       </c>
       <c r="P37" t="n">
-        <v>0.7286543937749114</v>
+        <v>0.7275138521428747</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.2020449087718715</v>
+        <v>0.1975781726699332</v>
       </c>
       <c r="R37" t="n">
-        <v>0.1433113444315184</v>
+        <v>0.1587960571826301</v>
       </c>
       <c r="S37" t="n">
-        <v>3.644287198781967</v>
+        <v>3.97806990146637</v>
       </c>
     </row>
     <row r="38">
@@ -2986,22 +2986,22 @@
         <v>2000</v>
       </c>
       <c r="N38" t="n">
-        <v>0.5491103784418376</v>
+        <v>0.549321434093842</v>
       </c>
       <c r="O38" t="n">
-        <v>0.5475927668295799</v>
+        <v>0.547568010040806</v>
       </c>
       <c r="P38" t="n">
-        <v>0.5654093347425969</v>
+        <v>0.5661944326352136</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.2196863615691374</v>
+        <v>0.2191665006201256</v>
       </c>
       <c r="R38" t="n">
-        <v>0.2131582591756341</v>
+        <v>0.2647406281301276</v>
       </c>
       <c r="S38" t="n">
-        <v>3.102766513824463</v>
+        <v>3.5118248462677</v>
       </c>
     </row>
     <row r="39">
@@ -3053,22 +3053,22 @@
         <v>2000</v>
       </c>
       <c r="N39" t="n">
-        <v>0.5548361686092774</v>
+        <v>0.5533840160215516</v>
       </c>
       <c r="O39" t="n">
-        <v>0.5567937501563427</v>
+        <v>0.5553220785342777</v>
       </c>
       <c r="P39" t="n">
-        <v>0.5722042877221712</v>
+        <v>0.5697105786656962</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.2034754673973338</v>
+        <v>0.2024471190288499</v>
       </c>
       <c r="R39" t="n">
-        <v>0.2156308227211205</v>
+        <v>0.2656796682913753</v>
       </c>
       <c r="S39" t="n">
-        <v>2.9824478328228</v>
+        <v>3.419738411903381</v>
       </c>
     </row>
     <row r="40">
@@ -3120,22 +3120,22 @@
         <v>2000</v>
       </c>
       <c r="N40" t="n">
-        <v>0.6032202688829342</v>
+        <v>0.6028024793047198</v>
       </c>
       <c r="O40" t="n">
-        <v>0.5957955837122769</v>
+        <v>0.5952466777846122</v>
       </c>
       <c r="P40" t="n">
-        <v>0.6395369925031316</v>
+        <v>0.6390055180737658</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.2134228545001998</v>
+        <v>0.2150184935904783</v>
       </c>
       <c r="R40" t="n">
-        <v>0.2111683000122144</v>
+        <v>0.2695940680743184</v>
       </c>
       <c r="S40" t="n">
-        <v>2.880117565393448</v>
+        <v>3.329272031784058</v>
       </c>
     </row>
     <row r="41">
@@ -3187,22 +3187,22 @@
         <v>2000</v>
       </c>
       <c r="N41" t="n">
-        <v>0.6268818494491175</v>
+        <v>0.6282079327951935</v>
       </c>
       <c r="O41" t="n">
-        <v>0.6218073975336268</v>
+        <v>0.6231846561010576</v>
       </c>
       <c r="P41" t="n">
-        <v>0.6714402988365168</v>
+        <v>0.673023882324545</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.2052018824339398</v>
+        <v>0.2088497440754659</v>
       </c>
       <c r="R41" t="n">
-        <v>0.2028491387214857</v>
+        <v>0.2627165825811354</v>
       </c>
       <c r="S41" t="n">
-        <v>2.819608002901077</v>
+        <v>3.273369967937469</v>
       </c>
     </row>
     <row r="42">
@@ -3254,22 +3254,22 @@
         <v>2000</v>
       </c>
       <c r="N42" t="n">
-        <v>0.6579863953844182</v>
+        <v>0.6584153830993659</v>
       </c>
       <c r="O42" t="n">
-        <v>0.6550991950102771</v>
+        <v>0.6557852032888601</v>
       </c>
       <c r="P42" t="n">
-        <v>0.7005660428294674</v>
+        <v>0.7010179982384855</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.2000778022832503</v>
+        <v>0.200994343279642</v>
       </c>
       <c r="R42" t="n">
-        <v>0.1948837405885769</v>
+        <v>0.251656140245667</v>
       </c>
       <c r="S42" t="n">
-        <v>2.692574054002762</v>
+        <v>3.150140404701233</v>
       </c>
     </row>
     <row r="43">
@@ -3321,22 +3321,22 @@
         <v>2000</v>
       </c>
       <c r="N43" t="n">
-        <v>0.6780174466908694</v>
+        <v>0.6784456266198076</v>
       </c>
       <c r="O43" t="n">
-        <v>0.6680049452098171</v>
+        <v>0.66867253526277</v>
       </c>
       <c r="P43" t="n">
-        <v>0.7274983454021253</v>
+        <v>0.7278635638513522</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.2090827481950066</v>
+        <v>0.2045850486669858</v>
       </c>
       <c r="R43" t="n">
-        <v>0.1956370427378145</v>
+        <v>0.2446932739852063</v>
       </c>
       <c r="S43" t="n">
-        <v>2.660438686609268</v>
+        <v>3.058496236801147</v>
       </c>
     </row>
     <row r="44">
@@ -3388,22 +3388,22 @@
         <v>2000</v>
       </c>
       <c r="N44" t="n">
-        <v>0.5494819243292204</v>
+        <v>0.5493727323425932</v>
       </c>
       <c r="O44" t="n">
-        <v>0.5478648491957069</v>
+        <v>0.5475627227753082</v>
       </c>
       <c r="P44" t="n">
-        <v>0.5661276039559501</v>
+        <v>0.5664685829769129</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.2319466955005019</v>
+        <v>0.2294915216510902</v>
       </c>
       <c r="R44" t="n">
-        <v>0.2190969920650024</v>
+        <v>0.2968212338888003</v>
       </c>
       <c r="S44" t="n">
-        <v>2.762349367141724</v>
+        <v>3.278376251459122</v>
       </c>
     </row>
     <row r="45">
@@ -3455,22 +3455,22 @@
         <v>2000</v>
       </c>
       <c r="N45" t="n">
-        <v>0.55193041273194</v>
+        <v>0.5506490802912719</v>
       </c>
       <c r="O45" t="n">
-        <v>0.5542325191402926</v>
+        <v>0.5528566418768249</v>
       </c>
       <c r="P45" t="n">
-        <v>0.5682240473899409</v>
+        <v>0.5660160335704725</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.2148344775592585</v>
+        <v>0.2126056199256447</v>
       </c>
       <c r="R45" t="n">
-        <v>0.2221307284265405</v>
+        <v>0.2981178475880177</v>
       </c>
       <c r="S45" t="n">
-        <v>2.65783280134201</v>
+        <v>3.20108163356781</v>
       </c>
     </row>
     <row r="46">
@@ -3522,22 +3522,22 @@
         <v>2000</v>
       </c>
       <c r="N46" t="n">
-        <v>0.6023853895415442</v>
+        <v>0.6048494382934591</v>
       </c>
       <c r="O46" t="n">
-        <v>0.5945773196561459</v>
+        <v>0.5969276888884544</v>
       </c>
       <c r="P46" t="n">
-        <v>0.6386907004883812</v>
+        <v>0.6417389893899069</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.2250817795694764</v>
+        <v>0.2250968450431687</v>
       </c>
       <c r="R46" t="n">
-        <v>0.2166441471508931</v>
+        <v>0.300445026517897</v>
       </c>
       <c r="S46" t="n">
-        <v>2.56521213054657</v>
+        <v>3.082648903131485</v>
       </c>
     </row>
     <row r="47">
@@ -3589,22 +3589,22 @@
         <v>2000</v>
       </c>
       <c r="N47" t="n">
-        <v>0.6278882095277534</v>
+        <v>0.628724465121996</v>
       </c>
       <c r="O47" t="n">
-        <v>0.622611399640848</v>
+        <v>0.6237963269955449</v>
       </c>
       <c r="P47" t="n">
-        <v>0.6723684584906315</v>
+        <v>0.6732052894295767</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.2170887722209718</v>
+        <v>0.2203757099575813</v>
       </c>
       <c r="R47" t="n">
-        <v>0.2081878997324984</v>
+        <v>0.2921659032336565</v>
       </c>
       <c r="S47" t="n">
-        <v>2.498994439840317</v>
+        <v>3.012552291154861</v>
       </c>
     </row>
     <row r="48">
@@ -3656,22 +3656,22 @@
         <v>2000</v>
       </c>
       <c r="N48" t="n">
-        <v>0.6576826217002584</v>
+        <v>0.6594608091197306</v>
       </c>
       <c r="O48" t="n">
-        <v>0.6547368651308422</v>
+        <v>0.6568602666686757</v>
       </c>
       <c r="P48" t="n">
-        <v>0.7001436590325967</v>
+        <v>0.7022736942138981</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.2127926969282051</v>
+        <v>0.2136450834314941</v>
       </c>
       <c r="R48" t="n">
-        <v>0.2013128813880407</v>
+        <v>0.2791863829194308</v>
       </c>
       <c r="S48" t="n">
-        <v>2.407725870609283</v>
+        <v>2.895447462797165</v>
       </c>
     </row>
     <row r="49">
@@ -3723,22 +3723,22 @@
         <v>2000</v>
       </c>
       <c r="N49" t="n">
-        <v>0.6785506656483716</v>
+        <v>0.6797513200998746</v>
       </c>
       <c r="O49" t="n">
-        <v>0.6686322783891834</v>
+        <v>0.6699426060268803</v>
       </c>
       <c r="P49" t="n">
-        <v>0.7280546220336547</v>
+        <v>0.7294552997595829</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.2218961955633222</v>
+        <v>0.2183885447446925</v>
       </c>
       <c r="R49" t="n">
-        <v>0.2021807994993216</v>
+        <v>0.2683462270722212</v>
       </c>
       <c r="S49" t="n">
-        <v>2.383969187736511</v>
+        <v>2.79380589723587</v>
       </c>
     </row>
     <row r="50">
@@ -3790,22 +3790,22 @@
         <v>2000</v>
       </c>
       <c r="N50" t="n">
-        <v>0.5558971367516043</v>
+        <v>0.548505059106575</v>
       </c>
       <c r="O50" t="n">
-        <v>0.5554728084642201</v>
+        <v>0.547299526597905</v>
       </c>
       <c r="P50" t="n">
-        <v>0.5753168705094621</v>
+        <v>0.5643343830069599</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.2286747012008622</v>
+        <v>0.227082452899042</v>
       </c>
       <c r="R50" t="n">
-        <v>0.001806224903680558</v>
+        <v>0.001696897992862777</v>
       </c>
       <c r="S50" t="n">
-        <v>11.12053179740906</v>
+        <v>9.769218802452087</v>
       </c>
     </row>
     <row r="51">
@@ -3857,22 +3857,22 @@
         <v>2000</v>
       </c>
       <c r="N51" t="n">
-        <v>0.5587893312481912</v>
+        <v>0.5567104754457826</v>
       </c>
       <c r="O51" t="n">
-        <v>0.5589971014315156</v>
+        <v>0.5584870119604541</v>
       </c>
       <c r="P51" t="n">
-        <v>0.5756726707508908</v>
+        <v>0.5745426659083828</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.2108110451079167</v>
+        <v>0.211572472270438</v>
       </c>
       <c r="R51" t="n">
-        <v>0.001922610832295137</v>
+        <v>0.001701841418150757</v>
       </c>
       <c r="S51" t="n">
-        <v>10.8729020357132</v>
+        <v>9.628194332122803</v>
       </c>
     </row>
     <row r="52">
@@ -3924,22 +3924,22 @@
         <v>2000</v>
       </c>
       <c r="N52" t="n">
-        <v>0.5909805038528317</v>
+        <v>0.6013983004291965</v>
       </c>
       <c r="O52" t="n">
-        <v>0.5871004933291282</v>
+        <v>0.5945046423731207</v>
       </c>
       <c r="P52" t="n">
-        <v>0.6248709591450925</v>
+        <v>0.6379783423301526</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.2333157078755795</v>
+        <v>0.2098342831580736</v>
       </c>
       <c r="R52" t="n">
-        <v>0.002941438049228596</v>
+        <v>0.001746732908126647</v>
       </c>
       <c r="S52" t="n">
-        <v>12.47606980800629</v>
+        <v>9.517356514930725</v>
       </c>
     </row>
     <row r="53">
@@ -3991,22 +3991,22 @@
         <v>2000</v>
       </c>
       <c r="N53" t="n">
-        <v>0.6231684502640095</v>
+        <v>0.6279957594598213</v>
       </c>
       <c r="O53" t="n">
-        <v>0.6197476109571666</v>
+        <v>0.6230198831834552</v>
       </c>
       <c r="P53" t="n">
-        <v>0.6667170789543324</v>
+        <v>0.6728628655494937</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.2276293599899412</v>
+        <v>0.1949870341191107</v>
       </c>
       <c r="R53" t="n">
-        <v>0.00413688863907395</v>
+        <v>0.00168551736428833</v>
       </c>
       <c r="S53" t="n">
-        <v>14.81796908378601</v>
+        <v>9.471415996551514</v>
       </c>
     </row>
     <row r="54">
@@ -4058,22 +4058,22 @@
         <v>2000</v>
       </c>
       <c r="N54" t="n">
-        <v>0.6553517143579002</v>
+        <v>0.6571669473486115</v>
       </c>
       <c r="O54" t="n">
-        <v>0.6538509095137787</v>
+        <v>0.6549980669563792</v>
       </c>
       <c r="P54" t="n">
-        <v>0.6973630218758382</v>
+        <v>0.6992396937873151</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.2112508453518398</v>
+        <v>0.1862967681798064</v>
       </c>
       <c r="R54" t="n">
-        <v>0.004712577766570475</v>
+        <v>0.00165188804556702</v>
       </c>
       <c r="S54" t="n">
-        <v>15.90003859996796</v>
+        <v>9.373443603515625</v>
       </c>
     </row>
     <row r="55">
@@ -4125,22 +4125,22 @@
         <v>2000</v>
       </c>
       <c r="N55" t="n">
-        <v>0.6781560398535581</v>
+        <v>0.6779357496686529</v>
       </c>
       <c r="O55" t="n">
-        <v>0.6685229809595186</v>
+        <v>0.6684541098025888</v>
       </c>
       <c r="P55" t="n">
-        <v>0.7279338528619866</v>
+        <v>0.727125436734848</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.2044346304745531</v>
+        <v>0.1887158946273344</v>
       </c>
       <c r="R55" t="n">
-        <v>0.005048580180979945</v>
+        <v>0.001675701383879867</v>
       </c>
       <c r="S55" t="n">
-        <v>16.2890430688858</v>
+        <v>9.356804609298706</v>
       </c>
     </row>
     <row r="56">
@@ -4192,22 +4192,22 @@
         <v>2000</v>
       </c>
       <c r="N56" t="n">
-        <v>0.548455226522074</v>
+        <v>0.5485094560993251</v>
       </c>
       <c r="O56" t="n">
-        <v>0.5479693098273051</v>
+        <v>0.54729910047441</v>
       </c>
       <c r="P56" t="n">
-        <v>0.5653913212458733</v>
+        <v>0.5643525497448829</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.2272952843724197</v>
+        <v>0.2268992837969585</v>
       </c>
       <c r="R56" t="n">
-        <v>0.01142807226388141</v>
+        <v>0.009113660337753786</v>
       </c>
       <c r="S56" t="n">
-        <v>9.235309481620789</v>
+        <v>7.829311549663544</v>
       </c>
     </row>
     <row r="57">
@@ -4259,22 +4259,22 @@
         <v>2000</v>
       </c>
       <c r="N57" t="n">
-        <v>0.5537633745646988</v>
+        <v>0.5567046726382392</v>
       </c>
       <c r="O57" t="n">
-        <v>0.5547110019441961</v>
+        <v>0.5584942908764867</v>
       </c>
       <c r="P57" t="n">
-        <v>0.5698271493658813</v>
+        <v>0.5745080788336226</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.2096203756359886</v>
+        <v>0.21140276214885</v>
       </c>
       <c r="R57" t="n">
-        <v>0.01145642216520344</v>
+        <v>0.009150177376606304</v>
       </c>
       <c r="S57" t="n">
-        <v>9.093986034393311</v>
+        <v>7.688688814640045</v>
       </c>
     </row>
     <row r="58">
@@ -4326,22 +4326,22 @@
         <v>2000</v>
       </c>
       <c r="N58" t="n">
-        <v>0.5938350493964445</v>
+        <v>0.6016176924438871</v>
       </c>
       <c r="O58" t="n">
-        <v>0.5893780714187025</v>
+        <v>0.5946247102787627</v>
       </c>
       <c r="P58" t="n">
-        <v>0.6285330709151068</v>
+        <v>0.6381589494151413</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.2300022774147878</v>
+        <v>0.2093039180813702</v>
       </c>
       <c r="R58" t="n">
-        <v>0.01352759099853829</v>
+        <v>0.009345812016998791</v>
       </c>
       <c r="S58" t="n">
-        <v>9.335792899131775</v>
+        <v>7.578289389610291</v>
       </c>
     </row>
     <row r="59">
@@ -4393,22 +4393,22 @@
         <v>2000</v>
       </c>
       <c r="N59" t="n">
-        <v>0.6224177956361067</v>
+        <v>0.6287325130760963</v>
       </c>
       <c r="O59" t="n">
-        <v>0.6188167368157295</v>
+        <v>0.6238128704929776</v>
       </c>
       <c r="P59" t="n">
-        <v>0.6659558299102702</v>
+        <v>0.6737230318770638</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.220057742343345</v>
+        <v>0.1943939657543439</v>
       </c>
       <c r="R59" t="n">
-        <v>0.01294509072403091</v>
+        <v>0.00901408165567788</v>
       </c>
       <c r="S59" t="n">
-        <v>9.171553611755371</v>
+        <v>7.532048404216766</v>
       </c>
     </row>
     <row r="60">
@@ -4460,22 +4460,22 @@
         <v>2000</v>
       </c>
       <c r="N60" t="n">
-        <v>0.6509610732546535</v>
+        <v>0.6572351111996911</v>
       </c>
       <c r="O60" t="n">
-        <v>0.64957111886037</v>
+        <v>0.6550372636215916</v>
       </c>
       <c r="P60" t="n">
-        <v>0.6916161159475013</v>
+        <v>0.6992618899768995</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.2073170792454689</v>
+        <v>0.1860215375667125</v>
       </c>
       <c r="R60" t="n">
-        <v>0.01202557735007335</v>
+        <v>0.008829037729986871</v>
       </c>
       <c r="S60" t="n">
-        <v>8.699127435684204</v>
+        <v>7.435247242450714</v>
       </c>
     </row>
     <row r="61">
@@ -4527,22 +4527,22 @@
         <v>2000</v>
       </c>
       <c r="N61" t="n">
-        <v>0.6637022318605257</v>
+        <v>0.6778657236496102</v>
       </c>
       <c r="O61" t="n">
-        <v>0.6543929392326234</v>
+        <v>0.6684215761722343</v>
       </c>
       <c r="P61" t="n">
-        <v>0.7106527940192362</v>
+        <v>0.7271392239679753</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.2038355944197775</v>
+        <v>0.1887052777488552</v>
       </c>
       <c r="R61" t="n">
-        <v>0.01154273518940827</v>
+        <v>0.008953101340366053</v>
       </c>
       <c r="S61" t="n">
-        <v>8.381094992160797</v>
+        <v>7.418764710426331</v>
       </c>
     </row>
     <row r="62">
@@ -4594,22 +4594,22 @@
         <v>2000</v>
       </c>
       <c r="N62" t="n">
-        <v>0.5479898781226893</v>
+        <v>0.5485820064797017</v>
       </c>
       <c r="O62" t="n">
-        <v>0.5474741213062942</v>
+        <v>0.547354930297495</v>
       </c>
       <c r="P62" t="n">
-        <v>0.564755532763739</v>
+        <v>0.5644817870616845</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.224727481622745</v>
+        <v>0.2268479772674065</v>
       </c>
       <c r="R62" t="n">
-        <v>0.03205713392110973</v>
+        <v>0.03011189081317458</v>
       </c>
       <c r="S62" t="n">
-        <v>7.025359690189362</v>
+        <v>6.386490643024445</v>
       </c>
     </row>
     <row r="63">
@@ -4661,22 +4661,22 @@
         <v>2000</v>
       </c>
       <c r="N63" t="n">
-        <v>0.5581909167202822</v>
+        <v>0.5566285107892326</v>
       </c>
       <c r="O63" t="n">
-        <v>0.5589622445337761</v>
+        <v>0.5584136756987726</v>
       </c>
       <c r="P63" t="n">
-        <v>0.5754696494191023</v>
+        <v>0.5744080457284485</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.2087758259833038</v>
+        <v>0.211392152406095</v>
       </c>
       <c r="R63" t="n">
-        <v>0.03224800467120632</v>
+        <v>0.03027116485856197</v>
       </c>
       <c r="S63" t="n">
-        <v>6.848342716693878</v>
+        <v>6.247596979141235</v>
       </c>
     </row>
     <row r="64">
@@ -4728,22 +4728,22 @@
         <v>2000</v>
       </c>
       <c r="N64" t="n">
-        <v>0.595210185947854</v>
+        <v>0.6015806022468262</v>
       </c>
       <c r="O64" t="n">
-        <v>0.5902547707291167</v>
+        <v>0.5945844302597855</v>
       </c>
       <c r="P64" t="n">
-        <v>0.6301538320646214</v>
+        <v>0.6381050744886546</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.2246007044760058</v>
+        <v>0.209351928837275</v>
       </c>
       <c r="R64" t="n">
-        <v>0.03329951378149082</v>
+        <v>0.03075216172725748</v>
       </c>
       <c r="S64" t="n">
-        <v>6.686493635177612</v>
+        <v>6.138925552368164</v>
       </c>
     </row>
     <row r="65">
@@ -4795,22 +4795,22 @@
         <v>2000</v>
       </c>
       <c r="N65" t="n">
-        <v>0.6226182628564237</v>
+        <v>0.6272970507174751</v>
       </c>
       <c r="O65" t="n">
-        <v>0.6189603199555571</v>
+        <v>0.6223178304254272</v>
       </c>
       <c r="P65" t="n">
-        <v>0.6659886335287969</v>
+        <v>0.6718567519097767</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.2142793257500084</v>
+        <v>0.195247801439223</v>
       </c>
       <c r="R65" t="n">
-        <v>0.03156497854289515</v>
+        <v>0.02967410771408183</v>
       </c>
       <c r="S65" t="n">
-        <v>6.508760452270508</v>
+        <v>6.094736993312836</v>
       </c>
     </row>
     <row r="66">
@@ -4862,22 +4862,22 @@
         <v>2000</v>
       </c>
       <c r="N66" t="n">
-        <v>0.6528415064507453</v>
+        <v>0.6563778766812206</v>
       </c>
       <c r="O66" t="n">
-        <v>0.6512382231034554</v>
+        <v>0.6543627474223302</v>
       </c>
       <c r="P66" t="n">
-        <v>0.6940185629142335</v>
+        <v>0.698195977321819</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.2023043799314319</v>
+        <v>0.1862827905682296</v>
       </c>
       <c r="R66" t="n">
-        <v>0.03012752562434606</v>
+        <v>0.0290213143951946</v>
       </c>
       <c r="S66" t="n">
-        <v>6.240396678447723</v>
+        <v>5.998845100402832</v>
       </c>
     </row>
     <row r="67">
@@ -4929,22 +4929,22 @@
         <v>2000</v>
       </c>
       <c r="N67" t="n">
-        <v>0.6759903393271229</v>
+        <v>0.678361741284496</v>
       </c>
       <c r="O67" t="n">
-        <v>0.666393399430773</v>
+        <v>0.6688944072171623</v>
       </c>
       <c r="P67" t="n">
-        <v>0.725185254257656</v>
+        <v>0.7275656248751119</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.2007807054775875</v>
+        <v>0.1886569900303917</v>
       </c>
       <c r="R67" t="n">
-        <v>0.03004480900298769</v>
+        <v>0.02939785049523916</v>
       </c>
       <c r="S67" t="n">
-        <v>6.110705971717834</v>
+        <v>5.979657053947449</v>
       </c>
     </row>
     <row r="68">
@@ -4996,22 +4996,22 @@
         <v>2000</v>
       </c>
       <c r="N68" t="n">
-        <v>0.5479994049403145</v>
+        <v>0.5486999924518291</v>
       </c>
       <c r="O68" t="n">
-        <v>0.5473173556431056</v>
+        <v>0.5474616304143457</v>
       </c>
       <c r="P68" t="n">
-        <v>0.5644486414411307</v>
+        <v>0.5646967549341323</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.221112916140276</v>
+        <v>0.2260230219733169</v>
       </c>
       <c r="R68" t="n">
-        <v>0.07127096450140995</v>
+        <v>0.06856457622858382</v>
       </c>
       <c r="S68" t="n">
-        <v>5.763629615306854</v>
+        <v>5.348176419734955</v>
       </c>
     </row>
     <row r="69">
@@ -5063,22 +5063,22 @@
         <v>2000</v>
       </c>
       <c r="N69" t="n">
-        <v>0.5586493385162076</v>
+        <v>0.5563166098837771</v>
       </c>
       <c r="O69" t="n">
-        <v>0.5600467194319241</v>
+        <v>0.5581296505787041</v>
       </c>
       <c r="P69" t="n">
-        <v>0.5761538042210169</v>
+        <v>0.5740239092005524</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.2077779815312831</v>
+        <v>0.2106323005256223</v>
       </c>
       <c r="R69" t="n">
-        <v>0.07190751963822156</v>
+        <v>0.06901233128033993</v>
       </c>
       <c r="S69" t="n">
-        <v>5.5603187084198</v>
+        <v>5.212331533432007</v>
       </c>
     </row>
     <row r="70">
@@ -5130,22 +5130,22 @@
         <v>2000</v>
       </c>
       <c r="N70" t="n">
-        <v>0.5958099274361787</v>
+        <v>0.6004455022537544</v>
       </c>
       <c r="O70" t="n">
-        <v>0.5903774161675938</v>
+        <v>0.5934052955504245</v>
       </c>
       <c r="P70" t="n">
-        <v>0.6306443197697612</v>
+        <v>0.636617995504983</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.2188052855290323</v>
+        <v>0.2100334201909576</v>
       </c>
       <c r="R70" t="n">
-        <v>0.07277091663318454</v>
+        <v>0.06981407008615331</v>
       </c>
       <c r="S70" t="n">
-        <v>5.418356359004974</v>
+        <v>5.108331084251404</v>
       </c>
     </row>
     <row r="71">
@@ -5197,22 +5197,22 @@
         <v>2000</v>
       </c>
       <c r="N71" t="n">
-        <v>0.6239366640644949</v>
+        <v>0.6284025469579831</v>
       </c>
       <c r="O71" t="n">
-        <v>0.6198613846805282</v>
+        <v>0.6233560142109623</v>
       </c>
       <c r="P71" t="n">
-        <v>0.6676712041442384</v>
+        <v>0.6735990286711411</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.2074749087853169</v>
+        <v>0.194996875643906</v>
       </c>
       <c r="R71" t="n">
-        <v>0.06962780435208843</v>
+        <v>0.06729979243848945</v>
       </c>
       <c r="S71" t="n">
-        <v>5.284556806087494</v>
+        <v>5.063023746013641</v>
       </c>
     </row>
     <row r="72">
@@ -5264,22 +5264,22 @@
         <v>2000</v>
       </c>
       <c r="N72" t="n">
-        <v>0.6545085571565005</v>
+        <v>0.6577411537028159</v>
       </c>
       <c r="O72" t="n">
-        <v>0.6526413863546713</v>
+        <v>0.6555571594768793</v>
       </c>
       <c r="P72" t="n">
-        <v>0.6961531388287907</v>
+        <v>0.7000757077953875</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.1961323131065679</v>
+        <v>0.1861085810587384</v>
       </c>
       <c r="R72" t="n">
-        <v>0.06646387285316428</v>
+        <v>0.06572163893907026</v>
       </c>
       <c r="S72" t="n">
-        <v>5.050640404224396</v>
+        <v>4.96602725982666</v>
       </c>
     </row>
     <row r="73">
@@ -5331,22 +5331,22 @@
         <v>2000</v>
       </c>
       <c r="N73" t="n">
-        <v>0.6778467582694528</v>
+        <v>0.678232630811886</v>
       </c>
       <c r="O73" t="n">
-        <v>0.6681310787819187</v>
+        <v>0.6687552899632705</v>
       </c>
       <c r="P73" t="n">
-        <v>0.7273201613290223</v>
+        <v>0.7275379635526443</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.1969927323883039</v>
+        <v>0.1888897152793352</v>
       </c>
       <c r="R73" t="n">
-        <v>0.06634879389499672</v>
+        <v>0.06649320913673358</v>
       </c>
       <c r="S73" t="n">
-        <v>4.953385531902313</v>
+        <v>4.94665253162384</v>
       </c>
     </row>
     <row r="74">
@@ -5398,22 +5398,22 @@
         <v>2000</v>
       </c>
       <c r="N74" t="n">
-        <v>0.5476666991555575</v>
+        <v>0.5487498250363302</v>
       </c>
       <c r="O74" t="n">
-        <v>0.5469149473237545</v>
+        <v>0.5475179202349015</v>
       </c>
       <c r="P74" t="n">
-        <v>0.5638705744657027</v>
+        <v>0.5648568384613306</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.2186245274245749</v>
+        <v>0.2246858735222383</v>
       </c>
       <c r="R74" t="n">
-        <v>0.1109467306657939</v>
+        <v>0.1103225510246016</v>
       </c>
       <c r="S74" t="n">
-        <v>4.978088855743408</v>
+        <v>4.736510157585144</v>
       </c>
     </row>
     <row r="75">
@@ -5465,22 +5465,22 @@
         <v>2000</v>
       </c>
       <c r="N75" t="n">
-        <v>0.5589873520556083</v>
+        <v>0.555782751589788</v>
       </c>
       <c r="O75" t="n">
-        <v>0.5604724201586553</v>
+        <v>0.5576628603073672</v>
       </c>
       <c r="P75" t="n">
-        <v>0.5768747884533271</v>
+        <v>0.573329848081189</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.206251386115566</v>
+        <v>0.2092877038345941</v>
       </c>
       <c r="R75" t="n">
-        <v>0.1124598994747331</v>
+        <v>0.1110819870473362</v>
       </c>
       <c r="S75" t="n">
-        <v>4.776382982730865</v>
+        <v>4.603926002979279</v>
       </c>
     </row>
     <row r="76">
@@ -5532,22 +5532,22 @@
         <v>2000</v>
       </c>
       <c r="N76" t="n">
-        <v>0.598502815705809</v>
+        <v>0.6022937137714502</v>
       </c>
       <c r="O76" t="n">
-        <v>0.5928283625090346</v>
+        <v>0.5951447792342721</v>
       </c>
       <c r="P76" t="n">
-        <v>0.6342347321831494</v>
+        <v>0.6389319440380116</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.2143001386560812</v>
+        <v>0.2093774871757104</v>
       </c>
       <c r="R76" t="n">
-        <v>0.1130517805641437</v>
+        <v>0.1120331173727546</v>
       </c>
       <c r="S76" t="n">
-        <v>4.648514568805695</v>
+        <v>4.505564332008362</v>
       </c>
     </row>
     <row r="77">
@@ -5599,22 +5599,22 @@
         <v>2000</v>
       </c>
       <c r="N77" t="n">
-        <v>0.624980703200964</v>
+        <v>0.6262438661786193</v>
       </c>
       <c r="O77" t="n">
-        <v>0.6208545599419619</v>
+        <v>0.6213002899059165</v>
       </c>
       <c r="P77" t="n">
-        <v>0.6693965946881928</v>
+        <v>0.6705257612348684</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.2027550492509918</v>
+        <v>0.1972763864962893</v>
       </c>
       <c r="R77" t="n">
-        <v>0.1081300293729261</v>
+        <v>0.1083442028094925</v>
       </c>
       <c r="S77" t="n">
-        <v>4.533490896224976</v>
+        <v>4.460037350654602</v>
       </c>
     </row>
     <row r="78">
@@ -5666,22 +5666,22 @@
         <v>2000</v>
       </c>
       <c r="N78" t="n">
-        <v>0.65580737488414</v>
+        <v>0.6569031828813897</v>
       </c>
       <c r="O78" t="n">
-        <v>0.6539528421262449</v>
+        <v>0.654781367862215</v>
       </c>
       <c r="P78" t="n">
-        <v>0.6975373650177037</v>
+        <v>0.6988126059306808</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.1920824430198564</v>
+        <v>0.1872460755799003</v>
       </c>
       <c r="R78" t="n">
-        <v>0.1026505401614496</v>
+        <v>0.1053484413481481</v>
       </c>
       <c r="S78" t="n">
-        <v>4.307101428508759</v>
+        <v>4.361832141876221</v>
       </c>
     </row>
     <row r="79">
@@ -5733,22 +5733,22 @@
         <v>2000</v>
       </c>
       <c r="N79" t="n">
-        <v>0.6782494078789484</v>
+        <v>0.6783347520896567</v>
       </c>
       <c r="O79" t="n">
-        <v>0.6684295439209418</v>
+        <v>0.6688605815771891</v>
       </c>
       <c r="P79" t="n">
-        <v>0.7277557247596871</v>
+        <v>0.7275115500171653</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.1942697907392759</v>
+        <v>0.1894652411217256</v>
       </c>
       <c r="R79" t="n">
-        <v>0.1026174147450646</v>
+        <v>0.1059793901749404</v>
       </c>
       <c r="S79" t="n">
-        <v>4.236488997936249</v>
+        <v>4.326996564865112</v>
       </c>
     </row>
     <row r="80">
@@ -5800,22 +5800,22 @@
         <v>2000</v>
       </c>
       <c r="N80" t="n">
-        <v>0.5478074029235604</v>
+        <v>0.549127966412838</v>
       </c>
       <c r="O80" t="n">
-        <v>0.5470282965723696</v>
+        <v>0.5478059309852813</v>
       </c>
       <c r="P80" t="n">
-        <v>0.564035159771867</v>
+        <v>0.5655357831556427</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.2174899310539811</v>
+        <v>0.2272004303044854</v>
       </c>
       <c r="R80" t="n">
-        <v>0.1533474606644806</v>
+        <v>0.1616754125000747</v>
       </c>
       <c r="S80" t="n">
-        <v>4.240300834178925</v>
+        <v>4.208856284618378</v>
       </c>
     </row>
     <row r="81">
@@ -5867,22 +5867,22 @@
         <v>2000</v>
       </c>
       <c r="N81" t="n">
-        <v>0.5584553071389765</v>
+        <v>0.5552401890844838</v>
       </c>
       <c r="O81" t="n">
-        <v>0.5600097112402784</v>
+        <v>0.5570894863834891</v>
       </c>
       <c r="P81" t="n">
-        <v>0.5761982804141016</v>
+        <v>0.5726186076396342</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.205955251035949</v>
+        <v>0.2115396987783777</v>
       </c>
       <c r="R81" t="n">
-        <v>0.1563096547510727</v>
+        <v>0.1627029244330505</v>
       </c>
       <c r="S81" t="n">
-        <v>4.058295488357544</v>
+        <v>4.080898970365524</v>
       </c>
     </row>
     <row r="82">
@@ -5934,22 +5934,22 @@
         <v>2000</v>
       </c>
       <c r="N82" t="n">
-        <v>0.5986679720549859</v>
+        <v>0.6017800495329084</v>
       </c>
       <c r="O82" t="n">
-        <v>0.5925899834024937</v>
+        <v>0.594476200263209</v>
       </c>
       <c r="P82" t="n">
-        <v>0.6341420178377755</v>
+        <v>0.6382578232569127</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.2109327862109278</v>
+        <v>0.2134534478067162</v>
       </c>
       <c r="R82" t="n">
-        <v>0.1552601588027759</v>
+        <v>0.1637669661150982</v>
       </c>
       <c r="S82" t="n">
-        <v>3.941085785627365</v>
+        <v>3.989366441965103</v>
       </c>
     </row>
     <row r="83">
@@ -6001,22 +6001,22 @@
         <v>2000</v>
       </c>
       <c r="N83" t="n">
-        <v>0.6244524647591064</v>
+        <v>0.6279204013441546</v>
       </c>
       <c r="O83" t="n">
-        <v>0.6202526218880982</v>
+        <v>0.6230656265424707</v>
       </c>
       <c r="P83" t="n">
-        <v>0.6684851888408353</v>
+        <v>0.6725809236729889</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.1999233657808594</v>
+        <v>0.2002322947917169</v>
       </c>
       <c r="R83" t="n">
-        <v>0.1484400447411457</v>
+        <v>0.1580951457991398</v>
       </c>
       <c r="S83" t="n">
-        <v>3.831219911575317</v>
+        <v>3.939672619104385</v>
       </c>
     </row>
     <row r="84">
@@ -6068,22 +6068,22 @@
         <v>2000</v>
       </c>
       <c r="N84" t="n">
-        <v>0.656245253536185</v>
+        <v>0.6579545361931527</v>
       </c>
       <c r="O84" t="n">
-        <v>0.6542751730622837</v>
+        <v>0.6557229812738538</v>
       </c>
       <c r="P84" t="n">
-        <v>0.6980706000842026</v>
+        <v>0.7002798464266325</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.1899167866500116</v>
+        <v>0.1901109892994904</v>
       </c>
       <c r="R84" t="n">
-        <v>0.1397615852621</v>
+        <v>0.1522598500151899</v>
       </c>
       <c r="S84" t="n">
-        <v>3.620415449142456</v>
+        <v>3.819873541593552</v>
       </c>
     </row>
     <row r="85">
@@ -6135,22 +6135,22 @@
         <v>2000</v>
       </c>
       <c r="N85" t="n">
-        <v>0.6775695719440755</v>
+        <v>0.6777388014900954</v>
       </c>
       <c r="O85" t="n">
-        <v>0.6678629483659047</v>
+        <v>0.6683349986737166</v>
       </c>
       <c r="P85" t="n">
-        <v>0.7269004432823505</v>
+        <v>0.7269170609111092</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.1938386434759456</v>
+        <v>0.1921630391899615</v>
       </c>
       <c r="R85" t="n">
-        <v>0.1394375081543561</v>
+        <v>0.1515721494580127</v>
       </c>
       <c r="S85" t="n">
-        <v>3.560867786407471</v>
+        <v>3.764781981706619</v>
       </c>
     </row>
     <row r="86">
@@ -6202,22 +6202,22 @@
         <v>2000</v>
       </c>
       <c r="N86" t="n">
-        <v>0.5487359012259548</v>
+        <v>0.5498783865088537</v>
       </c>
       <c r="O86" t="n">
-        <v>0.5475118616940899</v>
+        <v>0.5484239626603844</v>
       </c>
       <c r="P86" t="n">
-        <v>0.5651080794321774</v>
+        <v>0.5668359738832019</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.2199861246251973</v>
+        <v>0.2336469858152411</v>
       </c>
       <c r="R86" t="n">
-        <v>0.2136504626315587</v>
+        <v>0.2791775276938632</v>
       </c>
       <c r="S86" t="n">
-        <v>3.144358992576599</v>
+        <v>3.568026214838028</v>
       </c>
     </row>
     <row r="87">
@@ -6269,22 +6269,22 @@
         <v>2000</v>
       </c>
       <c r="N87" t="n">
-        <v>0.5567358627287847</v>
+        <v>0.5532599810103123</v>
       </c>
       <c r="O87" t="n">
-        <v>0.55852416073136</v>
+        <v>0.5552180693173112</v>
       </c>
       <c r="P87" t="n">
-        <v>0.5743723674367395</v>
+        <v>0.5697888012946906</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.2031367827403727</v>
+        <v>0.2168771462596034</v>
       </c>
       <c r="R87" t="n">
-        <v>0.2165270269365924</v>
+        <v>0.2799636037449417</v>
       </c>
       <c r="S87" t="n">
-        <v>2.991266489028931</v>
+        <v>3.454968124628067</v>
       </c>
     </row>
     <row r="88">
@@ -6336,22 +6336,22 @@
         <v>2000</v>
       </c>
       <c r="N88" t="n">
-        <v>0.5992782107688938</v>
+        <v>0.6015099209278988</v>
       </c>
       <c r="O88" t="n">
-        <v>0.5923289425665597</v>
+        <v>0.5939301522392487</v>
       </c>
       <c r="P88" t="n">
-        <v>0.6345073800500255</v>
+        <v>0.6376084212930654</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.2113496165949897</v>
+        <v>0.2267611485218529</v>
       </c>
       <c r="R88" t="n">
-        <v>0.211977587065515</v>
+        <v>0.2830041973804036</v>
       </c>
       <c r="S88" t="n">
-        <v>2.886644959449768</v>
+        <v>3.373668700456619</v>
       </c>
     </row>
     <row r="89">
@@ -6403,22 +6403,22 @@
         <v>2000</v>
       </c>
       <c r="N89" t="n">
-        <v>0.6230568763548914</v>
+        <v>0.6285693590975171</v>
       </c>
       <c r="O89" t="n">
-        <v>0.6185725869392296</v>
+        <v>0.6236743231560743</v>
       </c>
       <c r="P89" t="n">
-        <v>0.6667294401756679</v>
+        <v>0.6735477514553693</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.2022742991321153</v>
+        <v>0.2149206645355468</v>
       </c>
       <c r="R89" t="n">
-        <v>0.2041434377843495</v>
+        <v>0.272618220177768</v>
       </c>
       <c r="S89" t="n">
-        <v>2.822557091712952</v>
+        <v>3.315735459327698</v>
       </c>
     </row>
     <row r="90">
@@ -6470,22 +6470,22 @@
         <v>2000</v>
       </c>
       <c r="N90" t="n">
-        <v>0.6573706979904259</v>
+        <v>0.656234880776238</v>
       </c>
       <c r="O90" t="n">
-        <v>0.6550143113060063</v>
+        <v>0.6539686484641664</v>
       </c>
       <c r="P90" t="n">
-        <v>0.6997238407728226</v>
+        <v>0.6978996879427544</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.1948717677505665</v>
+        <v>0.2038832458783446</v>
       </c>
       <c r="R90" t="n">
-        <v>0.191947741370966</v>
+        <v>0.2565931262863645</v>
       </c>
       <c r="S90" t="n">
-        <v>2.664383113384247</v>
+        <v>3.168806344270706</v>
       </c>
     </row>
     <row r="91">
@@ -6537,22 +6537,22 @@
         <v>2000</v>
       </c>
       <c r="N91" t="n">
-        <v>0.6775812429472493</v>
+        <v>0.6771829699639439</v>
       </c>
       <c r="O91" t="n">
-        <v>0.6680529411532703</v>
+        <v>0.6677766775237846</v>
       </c>
       <c r="P91" t="n">
-        <v>0.7268178291810958</v>
+        <v>0.7262188038607776</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.203427176883632</v>
+        <v>0.2047109571244763</v>
       </c>
       <c r="R91" t="n">
-        <v>0.1925928667773871</v>
+        <v>0.2456752934313967</v>
       </c>
       <c r="S91" t="n">
-        <v>2.635956794023514</v>
+        <v>3.045904457569122</v>
       </c>
     </row>
     <row r="92">
@@ -6604,22 +6604,22 @@
         <v>2000</v>
       </c>
       <c r="N92" t="n">
-        <v>0.549604307294098</v>
+        <v>0.5500967704821083</v>
       </c>
       <c r="O92" t="n">
-        <v>0.5482563040282046</v>
+        <v>0.5485449434500224</v>
       </c>
       <c r="P92" t="n">
-        <v>0.5664864224372261</v>
+        <v>0.5673109267680966</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.2318293027479479</v>
+        <v>0.2440920047195279</v>
       </c>
       <c r="R92" t="n">
-        <v>0.218470775505094</v>
+        <v>0.3260439593537283</v>
       </c>
       <c r="S92" t="n">
-        <v>2.790382921695709</v>
+        <v>3.408146977424622</v>
       </c>
     </row>
     <row r="93">
@@ -6671,22 +6671,22 @@
         <v>2000</v>
       </c>
       <c r="N93" t="n">
-        <v>0.5541579654776472</v>
+        <v>0.5516366456000574</v>
       </c>
       <c r="O93" t="n">
-        <v>0.5560978090785922</v>
+        <v>0.5536947518711121</v>
       </c>
       <c r="P93" t="n">
-        <v>0.5710330422361285</v>
+        <v>0.5675332135433161</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.2139403596071971</v>
+        <v>0.226438980902755</v>
       </c>
       <c r="R93" t="n">
-        <v>0.2218732684388851</v>
+        <v>0.3268910866569563</v>
       </c>
       <c r="S93" t="n">
-        <v>2.661376714706421</v>
+        <v>3.306158721446991</v>
       </c>
     </row>
     <row r="94">
@@ -6738,22 +6738,22 @@
         <v>2000</v>
       </c>
       <c r="N94" t="n">
-        <v>0.6011215235813174</v>
+        <v>0.6012607867740556</v>
       </c>
       <c r="O94" t="n">
-        <v>0.5935442638858738</v>
+        <v>0.5934328965847558</v>
       </c>
       <c r="P94" t="n">
-        <v>0.6371544383106063</v>
+        <v>0.6371459628429572</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.2224858897231191</v>
+        <v>0.2391285471839486</v>
       </c>
       <c r="R94" t="n">
-        <v>0.2156893257254359</v>
+        <v>0.3314672426133631</v>
       </c>
       <c r="S94" t="n">
-        <v>2.565043538808823</v>
+        <v>3.22827997803688</v>
       </c>
     </row>
     <row r="95">
@@ -6805,22 +6805,22 @@
         <v>2000</v>
       </c>
       <c r="N95" t="n">
-        <v>0.628059411460433</v>
+        <v>0.6281742777144103</v>
       </c>
       <c r="O95" t="n">
-        <v>0.6227434439018551</v>
+        <v>0.6227027669184708</v>
       </c>
       <c r="P95" t="n">
-        <v>0.6728811136534378</v>
+        <v>0.6732565754301407</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.2137590207807536</v>
+        <v>0.2273503786523815</v>
       </c>
       <c r="R95" t="n">
-        <v>0.2064475782872666</v>
+        <v>0.318430190276385</v>
       </c>
       <c r="S95" t="n">
-        <v>2.48841181397438</v>
+        <v>3.163434743881226</v>
       </c>
     </row>
     <row r="96">
@@ -6872,22 +6872,22 @@
         <v>2000</v>
       </c>
       <c r="N96" t="n">
-        <v>0.6558622023295737</v>
+        <v>0.6562585899418311</v>
       </c>
       <c r="O96" t="n">
-        <v>0.653478632605791</v>
+        <v>0.6537622734558749</v>
       </c>
       <c r="P96" t="n">
-        <v>0.6976992661063905</v>
+        <v>0.6981129062146891</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.2085033176143231</v>
+        <v>0.2166502379731144</v>
       </c>
       <c r="R96" t="n">
-        <v>0.197729694989472</v>
+        <v>0.2965338653358074</v>
       </c>
       <c r="S96" t="n">
-        <v>2.387960582971573</v>
+        <v>3.004552006721497</v>
       </c>
     </row>
     <row r="97">
@@ -6939,22 +6939,22 @@
         <v>2000</v>
       </c>
       <c r="N97" t="n">
-        <v>0.6778350872662791</v>
+        <v>0.67764324515161</v>
       </c>
       <c r="O97" t="n">
-        <v>0.6682818852574811</v>
+        <v>0.6681275252467266</v>
       </c>
       <c r="P97" t="n">
-        <v>0.7269961131663761</v>
+        <v>0.7267734249460925</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.2162632086614494</v>
+        <v>0.2174538572585681</v>
       </c>
       <c r="R97" t="n">
-        <v>0.1983587021215356</v>
+        <v>0.2792702704600484</v>
       </c>
       <c r="S97" t="n">
-        <v>2.362474530935287</v>
+        <v>2.861600071191788</v>
       </c>
     </row>
     <row r="98">
@@ -7006,22 +7006,22 @@
         <v>2000</v>
       </c>
       <c r="N98" t="n">
-        <v>0.5556699587928496</v>
+        <v>0.5475589728331803</v>
       </c>
       <c r="O98" t="n">
-        <v>0.5541989928816475</v>
+        <v>0.5460412562354547</v>
       </c>
       <c r="P98" t="n">
-        <v>0.5741436681927609</v>
+        <v>0.5630115174109847</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.216715541865913</v>
+        <v>0.2187144165756999</v>
       </c>
       <c r="R98" t="n">
-        <v>0.001831368889112015</v>
+        <v>0.001842792396563201</v>
       </c>
       <c r="S98" t="n">
-        <v>11.10268640518188</v>
+        <v>11.0157665014267</v>
       </c>
     </row>
     <row r="99">
@@ -7073,22 +7073,22 @@
         <v>2000</v>
       </c>
       <c r="N99" t="n">
-        <v>0.5610705599636744</v>
+        <v>0.5579609804713765</v>
       </c>
       <c r="O99" t="n">
-        <v>0.562145067877022</v>
+        <v>0.5596576002547746</v>
       </c>
       <c r="P99" t="n">
-        <v>0.5800431717920586</v>
+        <v>0.5760795758263226</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.2034332744236162</v>
+        <v>0.2039048543158872</v>
       </c>
       <c r="R99" t="n">
-        <v>0.001926665108016818</v>
+        <v>0.00186654795946639</v>
       </c>
       <c r="S99" t="n">
-        <v>10.99303603172302</v>
+        <v>10.99484622478485</v>
       </c>
     </row>
     <row r="100">
@@ -7140,22 +7140,22 @@
         <v>2000</v>
       </c>
       <c r="N100" t="n">
-        <v>0.6042902860773898</v>
+        <v>0.6021551503937509</v>
       </c>
       <c r="O100" t="n">
-        <v>0.596871809787717</v>
+        <v>0.5950015041023951</v>
       </c>
       <c r="P100" t="n">
-        <v>0.6414492390365228</v>
+        <v>0.6387921520482784</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.2115033202293267</v>
+        <v>0.2131149247000535</v>
       </c>
       <c r="R100" t="n">
-        <v>0.002964001132921399</v>
+        <v>0.001904199533870417</v>
       </c>
       <c r="S100" t="n">
-        <v>12.87994647026062</v>
+        <v>10.89727389812469</v>
       </c>
     </row>
     <row r="101">
@@ -7207,22 +7207,22 @@
         <v>2000</v>
       </c>
       <c r="N101" t="n">
-        <v>0.6263188584781905</v>
+        <v>0.6270834141177211</v>
       </c>
       <c r="O101" t="n">
-        <v>0.6211647294540632</v>
+        <v>0.6218910917262314</v>
       </c>
       <c r="P101" t="n">
-        <v>0.6707113566142229</v>
+        <v>0.6714927092001942</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.2040127504195427</v>
+        <v>0.2046007476150653</v>
       </c>
       <c r="R101" t="n">
-        <v>0.004254372916363205</v>
+        <v>0.001842394508776866</v>
       </c>
       <c r="S101" t="n">
-        <v>15.4779908657074</v>
+        <v>10.7519599199295</v>
       </c>
     </row>
     <row r="102">
@@ -7274,22 +7274,22 @@
         <v>2000</v>
       </c>
       <c r="N102" t="n">
-        <v>0.6559525935233969</v>
+        <v>0.6566008910200795</v>
       </c>
       <c r="O102" t="n">
-        <v>0.6533579986024513</v>
+        <v>0.6540109350006048</v>
       </c>
       <c r="P102" t="n">
-        <v>0.6981934821140408</v>
+        <v>0.6987369150374313</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.2025608440477323</v>
+        <v>0.1994326147438883</v>
       </c>
       <c r="R102" t="n">
-        <v>0.004695030956174838</v>
+        <v>0.001790312309419123</v>
       </c>
       <c r="S102" t="n">
-        <v>16.14867079257965</v>
+        <v>10.42672419548035</v>
       </c>
     </row>
     <row r="103">
@@ -7341,22 +7341,22 @@
         <v>2000</v>
       </c>
       <c r="N103" t="n">
-        <v>0.6789679040118344</v>
+        <v>0.6784200963003649</v>
       </c>
       <c r="O103" t="n">
-        <v>0.6685087006770077</v>
+        <v>0.6680777822574917</v>
       </c>
       <c r="P103" t="n">
-        <v>0.7291568137420831</v>
+        <v>0.728267384733627</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.219181007727957</v>
+        <v>0.2066673747014695</v>
       </c>
       <c r="R103" t="n">
-        <v>0.005013255957174305</v>
+        <v>0.001783124710479818</v>
       </c>
       <c r="S103" t="n">
-        <v>16.36702144145966</v>
+        <v>10.13346898555756</v>
       </c>
     </row>
     <row r="104">
@@ -7408,22 +7408,22 @@
         <v>2000</v>
       </c>
       <c r="N104" t="n">
-        <v>0.547784685127685</v>
+        <v>0.5477157989079335</v>
       </c>
       <c r="O104" t="n">
-        <v>0.5461276340755893</v>
+        <v>0.5461921444024979</v>
       </c>
       <c r="P104" t="n">
-        <v>0.5633923780020151</v>
+        <v>0.5632587548440752</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.2183371707128558</v>
+        <v>0.2185930648864253</v>
       </c>
       <c r="R104" t="n">
-        <v>0.01125612875617581</v>
+        <v>0.009838054786934714</v>
       </c>
       <c r="S104" t="n">
-        <v>9.202493071556091</v>
+        <v>8.749364614486694</v>
       </c>
     </row>
     <row r="105">
@@ -7475,22 +7475,22 @@
         <v>2000</v>
       </c>
       <c r="N105" t="n">
-        <v>0.556216511453654</v>
+        <v>0.5580799380260154</v>
       </c>
       <c r="O105" t="n">
-        <v>0.5578136761632448</v>
+        <v>0.5597738621226892</v>
       </c>
       <c r="P105" t="n">
-        <v>0.5737489034535349</v>
+        <v>0.5761985375485846</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.2038279067618648</v>
+        <v>0.2040346503007162</v>
       </c>
       <c r="R105" t="n">
-        <v>0.01105789952690042</v>
+        <v>0.009975725775140099</v>
       </c>
       <c r="S105" t="n">
-        <v>9.040959119796753</v>
+        <v>8.691636204719543</v>
       </c>
     </row>
     <row r="106">
@@ -7542,22 +7542,22 @@
         <v>2000</v>
       </c>
       <c r="N106" t="n">
-        <v>0.6036289608656432</v>
+        <v>0.6020634746236569</v>
       </c>
       <c r="O106" t="n">
-        <v>0.5965070461029049</v>
+        <v>0.5950435838765431</v>
       </c>
       <c r="P106" t="n">
-        <v>0.6405071404233136</v>
+        <v>0.6388802808068225</v>
       </c>
       <c r="Q106" t="n">
-        <v>0.2122230864261257</v>
+        <v>0.2133570089040333</v>
       </c>
       <c r="R106" t="n">
-        <v>0.01267877564731013</v>
+        <v>0.01014818638657419</v>
       </c>
       <c r="S106" t="n">
-        <v>9.311433553695679</v>
+        <v>8.592013120651245</v>
       </c>
     </row>
     <row r="107">
@@ -7609,22 +7609,22 @@
         <v>2000</v>
       </c>
       <c r="N107" t="n">
-        <v>0.6222246447376989</v>
+        <v>0.6251270296391517</v>
       </c>
       <c r="O107" t="n">
-        <v>0.6172600658201729</v>
+        <v>0.620111643189842</v>
       </c>
       <c r="P107" t="n">
-        <v>0.665256844345562</v>
+        <v>0.6693134162621498</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.2055313555175562</v>
+        <v>0.2049813315955386</v>
       </c>
       <c r="R107" t="n">
-        <v>0.01180023653955479</v>
+        <v>0.009819204814615489</v>
       </c>
       <c r="S107" t="n">
-        <v>9.030341386795044</v>
+        <v>8.47254490852356</v>
       </c>
     </row>
     <row r="108">
@@ -7676,22 +7676,22 @@
         <v>2000</v>
       </c>
       <c r="N108" t="n">
-        <v>0.6496333599814476</v>
+        <v>0.6562948946016453</v>
       </c>
       <c r="O108" t="n">
-        <v>0.6470584770098822</v>
+        <v>0.6538307398680481</v>
       </c>
       <c r="P108" t="n">
-        <v>0.6902918653926747</v>
+        <v>0.698324031329192</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.2031779947292239</v>
+        <v>0.1993390461921809</v>
       </c>
       <c r="R108" t="n">
-        <v>0.01075817751392711</v>
+        <v>0.009537284648506332</v>
       </c>
       <c r="S108" t="n">
-        <v>8.475488305091858</v>
+        <v>8.202054977416992</v>
       </c>
     </row>
     <row r="109">
@@ -7743,22 +7743,22 @@
         <v>2000</v>
       </c>
       <c r="N109" t="n">
-        <v>0.6591622116259239</v>
+        <v>0.6786309037951914</v>
       </c>
       <c r="O109" t="n">
-        <v>0.6491243840591409</v>
+        <v>0.6683587792711017</v>
       </c>
       <c r="P109" t="n">
-        <v>0.7054403231509037</v>
+        <v>0.7284581903057672</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.2150664950639469</v>
+        <v>0.2059901794630649</v>
       </c>
       <c r="R109" t="n">
-        <v>0.01019931430747444</v>
+        <v>0.0095292183968207</v>
       </c>
       <c r="S109" t="n">
-        <v>8.166930735111237</v>
+        <v>8.001654803752899</v>
       </c>
     </row>
     <row r="110">
@@ -7810,22 +7810,22 @@
         <v>2000</v>
       </c>
       <c r="N110" t="n">
-        <v>0.5476256605565567</v>
+        <v>0.5479158620780628</v>
       </c>
       <c r="O110" t="n">
-        <v>0.5461019280708851</v>
+        <v>0.5463854279668312</v>
       </c>
       <c r="P110" t="n">
-        <v>0.5631841019259994</v>
+        <v>0.5635690560901999</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.2177693726186203</v>
+        <v>0.2175840835557192</v>
       </c>
       <c r="R110" t="n">
-        <v>0.03195812357887275</v>
+        <v>0.0321210104658947</v>
       </c>
       <c r="S110" t="n">
-        <v>6.990273237228394</v>
+        <v>7.025385737419128</v>
       </c>
     </row>
     <row r="111">
@@ -7877,22 +7877,22 @@
         <v>2000</v>
       </c>
       <c r="N111" t="n">
-        <v>0.5574321996339879</v>
+        <v>0.5580973464486455</v>
       </c>
       <c r="O111" t="n">
-        <v>0.5591660798194446</v>
+        <v>0.5598184610615334</v>
       </c>
       <c r="P111" t="n">
-        <v>0.5754511664182331</v>
+        <v>0.5762635875515931</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.2031399502096196</v>
+        <v>0.203172600485906</v>
       </c>
       <c r="R111" t="n">
-        <v>0.03241398014925413</v>
+        <v>0.03260820480078622</v>
       </c>
       <c r="S111" t="n">
-        <v>6.906844615936279</v>
+        <v>6.944861114025116</v>
       </c>
     </row>
     <row r="112">
@@ -7944,22 +7944,22 @@
         <v>2000</v>
       </c>
       <c r="N112" t="n">
-        <v>0.6021117618613401</v>
+        <v>0.6017786499028307</v>
       </c>
       <c r="O112" t="n">
-        <v>0.5950630142631195</v>
+        <v>0.5946896657662285</v>
       </c>
       <c r="P112" t="n">
-        <v>0.6390075331810391</v>
+        <v>0.6385143911445644</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.2119095337897842</v>
+        <v>0.2124171877118104</v>
       </c>
       <c r="R112" t="n">
-        <v>0.03273556975873921</v>
+        <v>0.0330832332524276</v>
       </c>
       <c r="S112" t="n">
-        <v>6.770117402076721</v>
+        <v>6.848071336746216</v>
       </c>
     </row>
     <row r="113">
@@ -8011,22 +8011,22 @@
         <v>2000</v>
       </c>
       <c r="N113" t="n">
-        <v>0.6257862302431872</v>
+        <v>0.6258710995773361</v>
       </c>
       <c r="O113" t="n">
-        <v>0.6205769310634384</v>
+        <v>0.6208399475319496</v>
       </c>
       <c r="P113" t="n">
-        <v>0.6702540800510804</v>
+        <v>0.6700245013315959</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.2039041258811248</v>
+        <v>0.2041080971942989</v>
       </c>
       <c r="R113" t="n">
-        <v>0.03156369220783479</v>
+        <v>0.03204241393539636</v>
       </c>
       <c r="S113" t="n">
-        <v>6.626412689685822</v>
+        <v>6.755282640457153</v>
       </c>
     </row>
     <row r="114">
@@ -8078,22 +8078,22 @@
         <v>2000</v>
       </c>
       <c r="N114" t="n">
-        <v>0.6568320553846109</v>
+        <v>0.656831314473186</v>
       </c>
       <c r="O114" t="n">
-        <v>0.6541632522775072</v>
+        <v>0.6542728652027537</v>
       </c>
       <c r="P114" t="n">
-        <v>0.6991756084714016</v>
+        <v>0.6989519456016657</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.2017367503772141</v>
+        <v>0.198753155188287</v>
       </c>
       <c r="R114" t="n">
-        <v>0.03069444921245335</v>
+        <v>0.0311925023965447</v>
       </c>
       <c r="S114" t="n">
-        <v>6.390286087989807</v>
+        <v>6.541535198688507</v>
       </c>
     </row>
     <row r="115">
@@ -8145,22 +8145,22 @@
         <v>2000</v>
       </c>
       <c r="N115" t="n">
-        <v>0.6766388094409662</v>
+        <v>0.6792027829507068</v>
       </c>
       <c r="O115" t="n">
-        <v>0.6663043156539684</v>
+        <v>0.6688353478621514</v>
       </c>
       <c r="P115" t="n">
-        <v>0.7262411524704007</v>
+        <v>0.7291347128034795</v>
       </c>
       <c r="Q115" t="n">
-        <v>0.210809511539524</v>
+        <v>0.2052765093452576</v>
       </c>
       <c r="R115" t="n">
-        <v>0.03108736980254355</v>
+        <v>0.03133072409331897</v>
       </c>
       <c r="S115" t="n">
-        <v>6.331404268741608</v>
+        <v>6.420167565345764</v>
       </c>
     </row>
     <row r="116">
@@ -8212,22 +8212,22 @@
         <v>2000</v>
       </c>
       <c r="N116" t="n">
-        <v>0.5478938771143123</v>
+        <v>0.548262491673195</v>
       </c>
       <c r="O116" t="n">
-        <v>0.5463665147344089</v>
+        <v>0.5466688319244047</v>
       </c>
       <c r="P116" t="n">
-        <v>0.5635815277325286</v>
+        <v>0.564112792051519</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.216759325548167</v>
+        <v>0.2158006855638178</v>
       </c>
       <c r="R116" t="n">
-        <v>0.07075249840676391</v>
+        <v>0.07204328312611818</v>
       </c>
       <c r="S116" t="n">
-        <v>5.698911309242249</v>
+        <v>5.774258553981781</v>
       </c>
     </row>
     <row r="117">
@@ -8279,22 +8279,22 @@
         <v>2000</v>
       </c>
       <c r="N117" t="n">
-        <v>0.5580908182901593</v>
+        <v>0.5575402769244829</v>
       </c>
       <c r="O117" t="n">
-        <v>0.5597784499099637</v>
+        <v>0.5593102273022181</v>
       </c>
       <c r="P117" t="n">
-        <v>0.5763118008757168</v>
+        <v>0.5755716411498372</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.2019062094476394</v>
+        <v>0.2015935062548231</v>
       </c>
       <c r="R117" t="n">
-        <v>0.0718876171673767</v>
+        <v>0.07320558044361354</v>
       </c>
       <c r="S117" t="n">
-        <v>5.598829448223114</v>
+        <v>5.680054485797882</v>
       </c>
     </row>
     <row r="118">
@@ -8346,22 +8346,22 @@
         <v>2000</v>
       </c>
       <c r="N118" t="n">
-        <v>0.601971798853563</v>
+        <v>0.6018206388051638</v>
       </c>
       <c r="O118" t="n">
-        <v>0.594935444353326</v>
+        <v>0.5947523506543906</v>
       </c>
       <c r="P118" t="n">
-        <v>0.6387949808070975</v>
+        <v>0.6382631322321892</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.2108764375155139</v>
+        <v>0.2111170339898477</v>
       </c>
       <c r="R118" t="n">
-        <v>0.07224745484502346</v>
+        <v>0.07415667086966864</v>
       </c>
       <c r="S118" t="n">
-        <v>5.466328024864197</v>
+        <v>5.588808417320251</v>
       </c>
     </row>
     <row r="119">
@@ -8413,22 +8413,22 @@
         <v>2000</v>
       </c>
       <c r="N119" t="n">
-        <v>0.6267015021140512</v>
+        <v>0.6245380657254462</v>
       </c>
       <c r="O119" t="n">
-        <v>0.6214203676804975</v>
+        <v>0.6196279165870023</v>
       </c>
       <c r="P119" t="n">
-        <v>0.6712482779012668</v>
+        <v>0.668429576123944</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.2020729258305274</v>
+        <v>0.2034790338959727</v>
       </c>
       <c r="R119" t="n">
-        <v>0.06962638212737339</v>
+        <v>0.07200871682056061</v>
       </c>
       <c r="S119" t="n">
-        <v>5.35606175661087</v>
+        <v>5.51955646276474</v>
       </c>
     </row>
     <row r="120">
@@ -8480,22 +8480,22 @@
         <v>2000</v>
       </c>
       <c r="N120" t="n">
-        <v>0.6586561793124194</v>
+        <v>0.6570669243062661</v>
       </c>
       <c r="O120" t="n">
-        <v>0.6558503635060199</v>
+        <v>0.6544410846777162</v>
       </c>
       <c r="P120" t="n">
-        <v>0.7016415961598857</v>
+        <v>0.6994186025993522</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.2000400553043072</v>
+        <v>0.1982304668193244</v>
       </c>
       <c r="R120" t="n">
-        <v>0.06765652740710898</v>
+        <v>0.07031898833736841</v>
       </c>
       <c r="S120" t="n">
-        <v>5.147069334983826</v>
+        <v>5.352474749088287</v>
       </c>
     </row>
     <row r="121">
@@ -8547,22 +8547,22 @@
         <v>2000</v>
       </c>
       <c r="N121" t="n">
-        <v>0.678585678657893</v>
+        <v>0.6786914471241554</v>
       </c>
       <c r="O121" t="n">
-        <v>0.6681950518619449</v>
+        <v>0.6684495198093695</v>
       </c>
       <c r="P121" t="n">
-        <v>0.7285373414230593</v>
+        <v>0.7284489200228986</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.2068914366892761</v>
+        <v>0.2042650076952162</v>
       </c>
       <c r="R121" t="n">
-        <v>0.06851496549206788</v>
+        <v>0.070944549558885</v>
       </c>
       <c r="S121" t="n">
-        <v>5.110719680786133</v>
+        <v>5.289279818534851</v>
       </c>
     </row>
     <row r="122">
@@ -8614,22 +8614,22 @@
         <v>2000</v>
       </c>
       <c r="N122" t="n">
-        <v>0.5478249908945608</v>
+        <v>0.5483284465644463</v>
       </c>
       <c r="O122" t="n">
-        <v>0.5463360448257637</v>
+        <v>0.5467790197897408</v>
       </c>
       <c r="P122" t="n">
-        <v>0.5635496368152799</v>
+        <v>0.5642869012772886</v>
       </c>
       <c r="Q122" t="n">
-        <v>0.2159412486904707</v>
+        <v>0.2145444759240445</v>
       </c>
       <c r="R122" t="n">
-        <v>0.1099676646793502</v>
+        <v>0.1142885134711121</v>
       </c>
       <c r="S122" t="n">
-        <v>4.904274344444275</v>
+        <v>5.030050158500671</v>
       </c>
     </row>
     <row r="123">
@@ -8681,22 +8681,22 @@
         <v>2000</v>
       </c>
       <c r="N123" t="n">
-        <v>0.5582228321617707</v>
+        <v>0.5586478878143217</v>
       </c>
       <c r="O123" t="n">
-        <v>0.5599305223341787</v>
+        <v>0.5602641591456624</v>
       </c>
       <c r="P123" t="n">
-        <v>0.5765679855302444</v>
+        <v>0.5769560061038363</v>
       </c>
       <c r="Q123" t="n">
-        <v>0.2007273209325704</v>
+        <v>0.199977972993935</v>
       </c>
       <c r="R123" t="n">
-        <v>0.1118865557518975</v>
+        <v>0.1160803236809391</v>
       </c>
       <c r="S123" t="n">
-        <v>4.796236157417297</v>
+        <v>4.92727792263031</v>
       </c>
     </row>
     <row r="124">
@@ -8748,22 +8748,22 @@
         <v>2000</v>
       </c>
       <c r="N124" t="n">
-        <v>0.6008569934966188</v>
+        <v>0.6040075608016802</v>
       </c>
       <c r="O124" t="n">
-        <v>0.5936992660189901</v>
+        <v>0.5967626767466847</v>
       </c>
       <c r="P124" t="n">
-        <v>0.6372384294757673</v>
+        <v>0.6408084541724963</v>
       </c>
       <c r="Q124" t="n">
-        <v>0.2098599274204334</v>
+        <v>0.2102325492780442</v>
       </c>
       <c r="R124" t="n">
-        <v>0.1119274910699016</v>
+        <v>0.1176484904115029</v>
       </c>
       <c r="S124" t="n">
-        <v>4.668303728103638</v>
+        <v>4.842430710792542</v>
       </c>
     </row>
     <row r="125">
@@ -8815,22 +8815,22 @@
         <v>2000</v>
       </c>
       <c r="N125" t="n">
-        <v>0.6265741981128279</v>
+        <v>0.6236125510039091</v>
       </c>
       <c r="O125" t="n">
-        <v>0.6215639400694458</v>
+        <v>0.6187806991453473</v>
       </c>
       <c r="P125" t="n">
-        <v>0.6705944971886711</v>
+        <v>0.6672621887159716</v>
       </c>
       <c r="Q125" t="n">
-        <v>0.2014204085062379</v>
+        <v>0.2030690573919586</v>
       </c>
       <c r="R125" t="n">
-        <v>0.1077710118285694</v>
+        <v>0.1144013621704748</v>
       </c>
       <c r="S125" t="n">
-        <v>4.556319057941437</v>
+        <v>4.786211907863617</v>
       </c>
     </row>
     <row r="126">
@@ -8882,22 +8882,22 @@
         <v>2000</v>
       </c>
       <c r="N126" t="n">
-        <v>0.6579211951790376</v>
+        <v>0.6576011214435326</v>
       </c>
       <c r="O126" t="n">
-        <v>0.6551384280172512</v>
+        <v>0.6548706154449654</v>
       </c>
       <c r="P126" t="n">
-        <v>0.7006801710613061</v>
+        <v>0.7001175418881471</v>
       </c>
       <c r="Q126" t="n">
-        <v>0.1984789680148169</v>
+        <v>0.1980708257761142</v>
       </c>
       <c r="R126" t="n">
-        <v>0.1046059474529002</v>
+        <v>0.1120428444891242</v>
       </c>
       <c r="S126" t="n">
-        <v>4.386231303215027</v>
+        <v>4.648784279823303</v>
       </c>
     </row>
     <row r="127">
@@ -8949,22 +8949,22 @@
         <v>2000</v>
       </c>
       <c r="N127" t="n">
-        <v>0.6788066982804966</v>
+        <v>0.6786440336737619</v>
       </c>
       <c r="O127" t="n">
-        <v>0.6684034462282062</v>
+        <v>0.6684278638374649</v>
       </c>
       <c r="P127" t="n">
-        <v>0.7288030950142899</v>
+        <v>0.7284309743624211</v>
       </c>
       <c r="Q127" t="n">
-        <v>0.2041001797766945</v>
+        <v>0.2026254898043731</v>
       </c>
       <c r="R127" t="n">
-        <v>0.105693241916788</v>
+        <v>0.1126155861308194</v>
       </c>
       <c r="S127" t="n">
-        <v>4.350977659225464</v>
+        <v>4.599559307098389</v>
       </c>
     </row>
     <row r="128">
@@ -9016,22 +9016,22 @@
         <v>2000</v>
       </c>
       <c r="N128" t="n">
-        <v>0.5481752846503182</v>
+        <v>0.5486311062320777</v>
       </c>
       <c r="O128" t="n">
-        <v>0.5467025171140205</v>
+        <v>0.547060574166455</v>
       </c>
       <c r="P128" t="n">
-        <v>0.564151541409228</v>
+        <v>0.564965449387104</v>
       </c>
       <c r="Q128" t="n">
-        <v>0.2160472919154504</v>
+        <v>0.2141744518461283</v>
       </c>
       <c r="R128" t="n">
-        <v>0.1518331011105881</v>
+        <v>0.1642565962394835</v>
       </c>
       <c r="S128" t="n">
-        <v>4.164517521858215</v>
+        <v>4.372471630573273</v>
       </c>
     </row>
     <row r="129">
@@ -9083,22 +9083,22 @@
         <v>2000</v>
       </c>
       <c r="N129" t="n">
-        <v>0.5574561362151043</v>
+        <v>0.5566052995590591</v>
       </c>
       <c r="O129" t="n">
-        <v>0.5592022061721386</v>
+        <v>0.558413724085983</v>
       </c>
       <c r="P129" t="n">
-        <v>0.5754635960568949</v>
+        <v>0.5742195040325164</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.2002095412995534</v>
+        <v>0.1991926545177148</v>
       </c>
       <c r="R129" t="n">
-        <v>0.1542127997391712</v>
+        <v>0.166372440832136</v>
       </c>
       <c r="S129" t="n">
-        <v>4.048919558525085</v>
+        <v>4.26818436384201</v>
       </c>
     </row>
     <row r="130">
@@ -9150,22 +9150,22 @@
         <v>2000</v>
       </c>
       <c r="N130" t="n">
-        <v>0.6031537864542401</v>
+        <v>0.6036163641949432</v>
       </c>
       <c r="O130" t="n">
-        <v>0.5959561305312064</v>
+        <v>0.5961676708871865</v>
       </c>
       <c r="P130" t="n">
-        <v>0.6402290725322491</v>
+        <v>0.6404724782494429</v>
       </c>
       <c r="Q130" t="n">
-        <v>0.2086293281340915</v>
+        <v>0.2102113755193189</v>
       </c>
       <c r="R130" t="n">
-        <v>0.1529316810317735</v>
+        <v>0.1688515885938523</v>
       </c>
       <c r="S130" t="n">
-        <v>3.921967715024948</v>
+        <v>4.19372683763504</v>
       </c>
     </row>
     <row r="131">
@@ -9217,22 +9217,22 @@
         <v>2000</v>
       </c>
       <c r="N131" t="n">
-        <v>0.6253165223766047</v>
+        <v>0.6226343587646244</v>
       </c>
       <c r="O131" t="n">
-        <v>0.6205109952591567</v>
+        <v>0.61787829753015</v>
       </c>
       <c r="P131" t="n">
-        <v>0.6690707436224196</v>
+        <v>0.6658012960639184</v>
       </c>
       <c r="Q131" t="n">
-        <v>0.2004658961339128</v>
+        <v>0.2032031874664649</v>
       </c>
       <c r="R131" t="n">
-        <v>0.1472388427411259</v>
+        <v>0.1644701550435848</v>
       </c>
       <c r="S131" t="n">
-        <v>3.829537838697433</v>
+        <v>4.145814716815948</v>
       </c>
     </row>
     <row r="132">
@@ -9284,22 +9284,22 @@
         <v>2000</v>
       </c>
       <c r="N132" t="n">
-        <v>0.6579167497104889</v>
+        <v>0.6573418024448595</v>
       </c>
       <c r="O132" t="n">
-        <v>0.6551183604929049</v>
+        <v>0.6547871158366784</v>
       </c>
       <c r="P132" t="n">
-        <v>0.700625171594556</v>
+        <v>0.6993855533074209</v>
       </c>
       <c r="Q132" t="n">
-        <v>0.1979332174424274</v>
+        <v>0.1969870283815875</v>
       </c>
       <c r="R132" t="n">
-        <v>0.1418111385423946</v>
+        <v>0.1603011187449545</v>
       </c>
       <c r="S132" t="n">
-        <v>3.664013475179672</v>
+        <v>4.027431815862656</v>
       </c>
     </row>
     <row r="133">
@@ -9351,22 +9351,22 @@
         <v>2000</v>
       </c>
       <c r="N133" t="n">
-        <v>0.6788774537372376</v>
+        <v>0.6781224857194335</v>
       </c>
       <c r="O133" t="n">
-        <v>0.6685214171658987</v>
+        <v>0.6681715693297952</v>
       </c>
       <c r="P133" t="n">
-        <v>0.7288322043348894</v>
+        <v>0.7275358717796171</v>
       </c>
       <c r="Q133" t="n">
-        <v>0.2033452510692975</v>
+        <v>0.199721940911379</v>
       </c>
       <c r="R133" t="n">
-        <v>0.1432862952460032</v>
+        <v>0.1593105788639703</v>
       </c>
       <c r="S133" t="n">
-        <v>3.638018399477005</v>
+        <v>3.96700394153595</v>
       </c>
     </row>
     <row r="134">
@@ -9418,22 +9418,22 @@
         <v>2000</v>
       </c>
       <c r="N134" t="n">
-        <v>0.5491081799454627</v>
+        <v>0.5492019824574645</v>
       </c>
       <c r="O134" t="n">
-        <v>0.547587762484834</v>
+        <v>0.5474825791229825</v>
       </c>
       <c r="P134" t="n">
-        <v>0.5653824898802444</v>
+        <v>0.5660044765708643</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.2194793588595005</v>
+        <v>0.2192274244797804</v>
       </c>
       <c r="R134" t="n">
-        <v>0.21246936303164</v>
+        <v>0.2647662657329724</v>
       </c>
       <c r="S134" t="n">
-        <v>3.097111463546753</v>
+        <v>3.510192543268204</v>
       </c>
     </row>
     <row r="135">
@@ -9485,22 +9485,22 @@
         <v>2000</v>
       </c>
       <c r="N135" t="n">
-        <v>0.5549725345865464</v>
+        <v>0.5533288893498897</v>
       </c>
       <c r="O135" t="n">
-        <v>0.5569080687494882</v>
+        <v>0.5553331378439434</v>
       </c>
       <c r="P135" t="n">
-        <v>0.5723614276773978</v>
+        <v>0.5695811152854375</v>
       </c>
       <c r="Q135" t="n">
-        <v>0.203295332077926</v>
+        <v>0.202492041791269</v>
       </c>
       <c r="R135" t="n">
-        <v>0.2149548044613236</v>
+        <v>0.2658093931408173</v>
       </c>
       <c r="S135" t="n">
-        <v>2.977348536252975</v>
+        <v>3.41892009973526</v>
       </c>
     </row>
     <row r="136">
@@ -9552,22 +9552,22 @@
         <v>2000</v>
       </c>
       <c r="N136" t="n">
-        <v>0.6037731227636536</v>
+        <v>0.6028962545199303</v>
       </c>
       <c r="O136" t="n">
-        <v>0.5961459624118626</v>
+        <v>0.5954285476607961</v>
       </c>
       <c r="P136" t="n">
-        <v>0.6403522979827809</v>
+        <v>0.6392403098883984</v>
       </c>
       <c r="Q136" t="n">
-        <v>0.2129696877388117</v>
+        <v>0.2153389278474014</v>
       </c>
       <c r="R136" t="n">
-        <v>0.2091016151834814</v>
+        <v>0.269339683959719</v>
       </c>
       <c r="S136" t="n">
-        <v>2.866974711418152</v>
+        <v>3.323893398046494</v>
       </c>
     </row>
     <row r="137">
@@ -9619,22 +9619,22 @@
         <v>2000</v>
       </c>
       <c r="N137" t="n">
-        <v>0.6274514251097632</v>
+        <v>0.627370213936569</v>
       </c>
       <c r="O137" t="n">
-        <v>0.6223010487856295</v>
+        <v>0.6225549941859077</v>
       </c>
       <c r="P137" t="n">
-        <v>0.6722326945919346</v>
+        <v>0.6719289395761655</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.2054928890911357</v>
+        <v>0.2080815178528859</v>
       </c>
       <c r="R137" t="n">
-        <v>0.2013021763239785</v>
+        <v>0.2599049388875832</v>
       </c>
       <c r="S137" t="n">
-        <v>2.808071315288544</v>
+        <v>3.255889117717743</v>
       </c>
     </row>
     <row r="138">
@@ -9686,22 +9686,22 @@
         <v>2000</v>
       </c>
       <c r="N138" t="n">
-        <v>0.6574610891842491</v>
+        <v>0.6575877850378865</v>
       </c>
       <c r="O138" t="n">
-        <v>0.6546958485905738</v>
+        <v>0.6553210901317642</v>
       </c>
       <c r="P138" t="n">
-        <v>0.6998662585033776</v>
+        <v>0.699679751756715</v>
       </c>
       <c r="Q138" t="n">
-        <v>0.2035167404246266</v>
+        <v>0.1984210830668538</v>
       </c>
       <c r="R138" t="n">
-        <v>0.1944875466171473</v>
+        <v>0.2449873672768092</v>
       </c>
       <c r="S138" t="n">
-        <v>2.685610622167587</v>
+        <v>3.104597330093384</v>
       </c>
     </row>
     <row r="139">
@@ -9753,22 +9753,22 @@
         <v>2000</v>
       </c>
       <c r="N139" t="n">
-        <v>0.6779809748059513</v>
+        <v>0.6773653293885342</v>
       </c>
       <c r="O139" t="n">
-        <v>0.6678829672874905</v>
+        <v>0.6679288020883146</v>
       </c>
       <c r="P139" t="n">
-        <v>0.7274882658573815</v>
+        <v>0.7262397102657255</v>
       </c>
       <c r="Q139" t="n">
-        <v>0.210455539881806</v>
+        <v>0.1999314285745515</v>
       </c>
       <c r="R139" t="n">
-        <v>0.1960305414880452</v>
+        <v>0.2344510814480389</v>
       </c>
       <c r="S139" t="n">
-        <v>2.663760304450989</v>
+        <v>2.994053840637207</v>
       </c>
     </row>
     <row r="140">
@@ -9820,22 +9820,22 @@
         <v>2000</v>
       </c>
       <c r="N140" t="n">
-        <v>0.5494577408690949</v>
+        <v>0.5491624095227138</v>
       </c>
       <c r="O140" t="n">
-        <v>0.5478384762929982</v>
+        <v>0.5473881645865513</v>
       </c>
       <c r="P140" t="n">
-        <v>0.566124037163291</v>
+        <v>0.5661866926883249</v>
       </c>
       <c r="Q140" t="n">
-        <v>0.2316972472948654</v>
+        <v>0.2294891413394506</v>
       </c>
       <c r="R140" t="n">
-        <v>0.2184506225068639</v>
+        <v>0.2965984228026973</v>
       </c>
       <c r="S140" t="n">
-        <v>2.758856803178787</v>
+        <v>3.275004863739014</v>
       </c>
     </row>
     <row r="141">
@@ -9887,22 +9887,22 @@
         <v>2000</v>
       </c>
       <c r="N141" t="n">
-        <v>0.5519282366791113</v>
+        <v>0.5504633904498845</v>
       </c>
       <c r="O141" t="n">
-        <v>0.5542484091823024</v>
+        <v>0.5526931639880758</v>
       </c>
       <c r="P141" t="n">
-        <v>0.5682008026127581</v>
+        <v>0.5657517729813025</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.2146304532239482</v>
+        <v>0.2125733883565176</v>
       </c>
       <c r="R141" t="n">
-        <v>0.2215272777085008</v>
+        <v>0.29799095237529</v>
       </c>
       <c r="S141" t="n">
-        <v>2.655000030994415</v>
+        <v>3.198568850755692</v>
       </c>
     </row>
     <row r="142">
@@ -9954,22 +9954,22 @@
         <v>2000</v>
       </c>
       <c r="N142" t="n">
-        <v>0.6023287045233945</v>
+        <v>0.6033402871621031</v>
       </c>
       <c r="O142" t="n">
-        <v>0.5944873921470215</v>
+        <v>0.5956081079063889</v>
       </c>
       <c r="P142" t="n">
-        <v>0.6386215745098031</v>
+        <v>0.6397903661146231</v>
       </c>
       <c r="Q142" t="n">
-        <v>0.225010060783333</v>
+        <v>0.2253506128385802</v>
       </c>
       <c r="R142" t="n">
-        <v>0.2153590183013278</v>
+        <v>0.299215169693877</v>
       </c>
       <c r="S142" t="n">
-        <v>2.55840465426445</v>
+        <v>3.073744177818298</v>
       </c>
     </row>
     <row r="143">
@@ -10021,22 +10021,22 @@
         <v>2000</v>
       </c>
       <c r="N143" t="n">
-        <v>0.6282401246115947</v>
+        <v>0.6268383173337567</v>
       </c>
       <c r="O143" t="n">
-        <v>0.6229314129614723</v>
+        <v>0.6218846422365431</v>
       </c>
       <c r="P143" t="n">
-        <v>0.672992058620793</v>
+        <v>0.6710463522285166</v>
       </c>
       <c r="Q143" t="n">
-        <v>0.2178908459655909</v>
+        <v>0.219929935922296</v>
       </c>
       <c r="R143" t="n">
-        <v>0.2069974742388078</v>
+        <v>0.2879389571022353</v>
       </c>
       <c r="S143" t="n">
-        <v>2.489576607942581</v>
+        <v>2.98746395111084</v>
       </c>
     </row>
     <row r="144">
@@ -10088,22 +10088,22 @@
         <v>2000</v>
       </c>
       <c r="N144" t="n">
-        <v>0.6565468044860705</v>
+        <v>0.6583183237027197</v>
       </c>
       <c r="O144" t="n">
-        <v>0.653813165100125</v>
+        <v>0.6558117160746137</v>
       </c>
       <c r="P144" t="n">
-        <v>0.698606502902287</v>
+        <v>0.7007448981676453</v>
       </c>
       <c r="Q144" t="n">
-        <v>0.2154438002008535</v>
+        <v>0.2104196991457495</v>
       </c>
       <c r="R144" t="n">
-        <v>0.2013168732131148</v>
+        <v>0.2658560782335053</v>
       </c>
       <c r="S144" t="n">
-        <v>2.409514874219894</v>
+        <v>2.815064311027527</v>
       </c>
     </row>
     <row r="145">
@@ -10155,22 +10155,22 @@
         <v>2000</v>
       </c>
       <c r="N145" t="n">
-        <v>0.6784602153737748</v>
+        <v>0.6787403194499456</v>
       </c>
       <c r="O145" t="n">
-        <v>0.6684494717713614</v>
+        <v>0.6692219980377853</v>
       </c>
       <c r="P145" t="n">
-        <v>0.7281527932539045</v>
+        <v>0.7280307493723317</v>
       </c>
       <c r="Q145" t="n">
-        <v>0.2225898442186999</v>
+        <v>0.2116972101944904</v>
       </c>
       <c r="R145" t="n">
-        <v>0.2024718504465857</v>
+        <v>0.2472858963268751</v>
       </c>
       <c r="S145" t="n">
-        <v>2.388127386569977</v>
+        <v>2.671275645494461</v>
       </c>
     </row>
   </sheetData>
